--- a/data/credit_bond_all_2026-09-17.xlsx
+++ b/data/credit_bond_all_2026-09-17.xlsx
@@ -14408,7 +14408,7 @@
     <row r="62" customHeight="true" ht="18.0">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>26电投K7</t>
+          <t>26富开01</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -14418,64 +14418,64 @@
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>246128.SH</t>
+          <t>284033.SH</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>20Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E62" s="4" t="n">
-        <v>20.0</v>
+        <v>10.0</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>20.0</v>
+        <v>10.0</v>
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.70</t>
+          <t>1.30 ~ 2.30</t>
         </is>
       </c>
       <c r="H62" s="4" t="n">
-        <v>2.25</v>
+        <v>1.94</v>
       </c>
       <c r="I62" s="4" t="n">
-        <v>11.76</v>
+        <v>52.94</v>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>26电投K6</t>
+          <t>24富开02</t>
         </is>
       </c>
       <c r="L62" s="3" t="inlineStr">
         <is>
-          <t>9.92Y</t>
+          <t>2.45Y</t>
         </is>
       </c>
       <c r="M62" s="3" t="inlineStr">
         <is>
-          <t>1.9686</t>
+          <t>1.6772</t>
         </is>
       </c>
       <c r="N62" s="3" t="inlineStr">
         <is>
-          <t>--/1.9700</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O62" s="3" t="inlineStr">
         <is>
-          <t>国家电力投资集团有限公司</t>
+          <t>杭州富阳开发区建设投资集团有限公司</t>
         </is>
       </c>
       <c r="P62" s="3" t="inlineStr">
         <is>
-          <t>B- 44.43</t>
+          <t>C 26.11</t>
         </is>
       </c>
       <c r="Q62" s="3" t="inlineStr">
@@ -14495,42 +14495,42 @@
       </c>
       <c r="T62" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="U62" s="4" t="n">
-        <v>3.99</v>
+        <v>3.71</v>
       </c>
       <c r="V62" s="3"/>
       <c r="W62" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X62" s="3" t="inlineStr">
         <is>
-          <t>2.20%~2.30%</t>
+          <t>1.90%~2.00%</t>
         </is>
       </c>
       <c r="Y62" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z62" s="3"/>
       <c r="AA62" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>浙江省-杭州市</t>
         </is>
       </c>
       <c r="AB62" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行等相关费用后,拟用于生产性支出,包括偿还有息债务、补充流动资金等符合法律法规要求的用途</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟全部用于置换发行人为偿还公司债券本金而使用的自有资金[21富开01]</t>
         </is>
       </c>
       <c r="AC62" s="3" t="inlineStr">
         <is>
-          <t>东方证券股份有限公司,中银国际证券股份有限公司,国泰海通证券股份有限公司,中泰证券股份有限公司,光大证券股份有限公司,平安证券股份有限公司</t>
+          <t>财通证券股份有限公司,国泰海通证券股份有限公司</t>
         </is>
       </c>
       <c r="AD62" s="3"/>
@@ -14541,7 +14541,7 @@
       </c>
       <c r="AF62" s="3" t="inlineStr">
         <is>
-          <t>中央国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG62" s="3" t="inlineStr">
@@ -14551,23 +14551,27 @@
       </c>
       <c r="AH62" s="3" t="inlineStr">
         <is>
-          <t>国家电力投资集团有限公司2026年面向专业投资者公开发行科技创新公司债券(第七期)</t>
+          <t>杭州富阳开发区建设投资集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI62" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ62" s="3" t="inlineStr">
         <is>
-          <t>2046-09-18</t>
-        </is>
-      </c>
-      <c r="AK62" s="3"/>
+          <t>2031-09-21</t>
+        </is>
+      </c>
+      <c r="AK62" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL62" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t/>
         </is>
       </c>
       <c r="AM62" s="3" t="inlineStr">
@@ -14577,37 +14581,37 @@
       </c>
       <c r="AN62" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="AO62" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP62" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ62" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR62" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS62" s="3" t="inlineStr">
         <is>
-          <t>其他电力</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT62" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU62" s="3" t="inlineStr">
@@ -14640,7 +14644,7 @@
     <row r="63" customHeight="true" ht="18.0">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>26富开01</t>
+          <t>26嘉铁01</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -14650,7 +14654,7 @@
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>284033.SH</t>
+          <t>283974.SH</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
@@ -14659,21 +14663,21 @@
         </is>
       </c>
       <c r="E63" s="4" t="n">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H63" s="4" t="n">
-        <v>1.94</v>
+        <v>1.81</v>
       </c>
       <c r="I63" s="4" t="n">
-        <v>52.94</v>
+        <v>39.94</v>
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
@@ -14682,17 +14686,17 @@
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>24富开02</t>
+          <t>26嘉铁Z1</t>
         </is>
       </c>
       <c r="L63" s="3" t="inlineStr">
         <is>
-          <t>2.45Y</t>
+          <t>2.75Y</t>
         </is>
       </c>
       <c r="M63" s="3" t="inlineStr">
         <is>
-          <t>1.6772</t>
+          <t>1.6883</t>
         </is>
       </c>
       <c r="N63" s="3" t="inlineStr">
@@ -14702,12 +14706,12 @@
       </c>
       <c r="O63" s="3" t="inlineStr">
         <is>
-          <t>杭州富阳开发区建设投资集团有限公司</t>
+          <t>嘉兴市铁路与轨道交通投资集团有限责任公司</t>
         </is>
       </c>
       <c r="P63" s="3" t="inlineStr">
         <is>
-          <t>C 26.11</t>
+          <t>C- 14.50</t>
         </is>
       </c>
       <c r="Q63" s="3" t="inlineStr">
@@ -14717,7 +14721,7 @@
       </c>
       <c r="R63" s="3" t="inlineStr">
         <is>
-          <t>09-17 15:00</t>
+          <t>09-17 16:00</t>
         </is>
       </c>
       <c r="S63" s="3" t="inlineStr">
@@ -14731,38 +14735,38 @@
         </is>
       </c>
       <c r="U63" s="4" t="n">
-        <v>3.71</v>
+        <v>4.3333</v>
       </c>
       <c r="V63" s="3"/>
       <c r="W63" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X63" s="3" t="inlineStr">
         <is>
-          <t>1.90%~2.00%</t>
+          <t>1.76%~1.86%</t>
         </is>
       </c>
       <c r="Y63" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z63" s="3"/>
       <c r="AA63" s="3" t="inlineStr">
         <is>
-          <t>浙江省-杭州市</t>
+          <t>浙江省-嘉兴市</t>
         </is>
       </c>
       <c r="AB63" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟全部用于置换发行人为偿还公司债券本金而使用的自有资金[21富开01]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还有息债务</t>
         </is>
       </c>
       <c r="AC63" s="3" t="inlineStr">
         <is>
-          <t>财通证券股份有限公司,国泰海通证券股份有限公司</t>
+          <t>中信建投证券股份有限公司</t>
         </is>
       </c>
       <c r="AD63" s="3"/>
@@ -14783,7 +14787,7 @@
       </c>
       <c r="AH63" s="3" t="inlineStr">
         <is>
-          <t>杭州富阳开发区建设投资集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>嘉兴市铁路与轨道交通投资集团有限责任公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI63" s="3" t="inlineStr">
@@ -14823,7 +14827,7 @@
       </c>
       <c r="AP63" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ63" s="3" t="inlineStr">
@@ -14833,12 +14837,12 @@
       </c>
       <c r="AR63" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AS63" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AT63" s="3" t="inlineStr">
@@ -14876,7 +14880,7 @@
     <row r="64" customHeight="true" ht="18.0">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>26嘉铁01</t>
+          <t>26点创01(取消发行)</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -14886,64 +14890,58 @@
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>283974.SH</t>
+          <t>DY283983.SH</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>1.01Y</t>
         </is>
       </c>
       <c r="E64" s="4" t="n">
-        <v>6.0</v>
-      </c>
-      <c r="F64" s="4" t="n">
-        <v>6.0</v>
-      </c>
+        <v>2.0</v>
+      </c>
+      <c r="F64" s="3"/>
       <c r="G64" s="3" t="inlineStr">
         <is>
           <t>1.50 ~ 2.50</t>
         </is>
       </c>
-      <c r="H64" s="4" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="I64" s="4" t="n">
-        <v>39.94</v>
-      </c>
+      <c r="H64" s="3"/>
+      <c r="I64" s="3"/>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>--</t>
         </is>
       </c>
       <c r="K64" s="3" t="inlineStr">
         <is>
-          <t>26嘉铁Z1</t>
+          <t>25平安点创MTN003</t>
         </is>
       </c>
       <c r="L64" s="3" t="inlineStr">
         <is>
-          <t>2.75Y</t>
+          <t>1.11Y</t>
         </is>
       </c>
       <c r="M64" s="3" t="inlineStr">
         <is>
-          <t>1.6883</t>
+          <t>1.7155</t>
         </is>
       </c>
       <c r="N64" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.6500</t>
         </is>
       </c>
       <c r="O64" s="3" t="inlineStr">
         <is>
-          <t>嘉兴市铁路与轨道交通投资集团有限责任公司</t>
+          <t>平安点创国际融资租赁有限公司</t>
         </is>
       </c>
       <c r="P64" s="3" t="inlineStr">
         <is>
-          <t>C- 14.50</t>
+          <t>C- 11.60</t>
         </is>
       </c>
       <c r="Q64" s="3" t="inlineStr">
@@ -14953,7 +14951,7 @@
       </c>
       <c r="R64" s="3" t="inlineStr">
         <is>
-          <t>09-17 16:00</t>
+          <t>09-17 15:00</t>
         </is>
       </c>
       <c r="S64" s="3" t="inlineStr">
@@ -14966,13 +14964,11 @@
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="U64" s="4" t="n">
-        <v>4.3333</v>
-      </c>
+      <c r="U64" s="3"/>
       <c r="V64" s="3"/>
       <c r="W64" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X64" s="3" t="inlineStr">
@@ -14985,20 +14981,24 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z64" s="3"/>
+      <c r="Z64" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA64" s="3" t="inlineStr">
         <is>
-          <t>浙江省-嘉兴市</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="AB64" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还有息债务</t>
+          <t>本期债券募集资金扣除发行费用后,拟将不低于70%的部分用于支持中小微企业发展,具体方式为向中小微企业投放保理款(含置换3个月内投放或新增投放),剩余部分用于偿还有息负债。</t>
         </is>
       </c>
       <c r="AC64" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司</t>
+          <t>国泰海通证券股份有限公司,中信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD64" s="3"/>
@@ -15009,7 +15009,7 @@
       </c>
       <c r="AF64" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>外商独资企业</t>
         </is>
       </c>
       <c r="AG64" s="3" t="inlineStr">
@@ -15019,7 +15019,7 @@
       </c>
       <c r="AH64" s="3" t="inlineStr">
         <is>
-          <t>嘉兴市铁路与轨道交通投资集团有限责任公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>平安点创国际融资租赁有限公司2026年面向专业投资者非公开发行中小微企业支持公司债券(第一期)(品种一)(取消发行)</t>
         </is>
       </c>
       <c r="AI64" s="3" t="inlineStr">
@@ -15029,7 +15029,7 @@
       </c>
       <c r="AJ64" s="3" t="inlineStr">
         <is>
-          <t>2031-09-21</t>
+          <t>2027-09-26</t>
         </is>
       </c>
       <c r="AK64" s="3" t="inlineStr">
@@ -15054,32 +15054,32 @@
       </c>
       <c r="AO64" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP64" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ64" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR64" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AS64" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AT64" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU64" s="3" t="inlineStr">
@@ -15112,7 +15112,7 @@
     <row r="65" customHeight="true" ht="18.0">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>26点创01(取消发行)</t>
+          <t>26恒信G3</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -15122,90 +15122,98 @@
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>DY283983.SH</t>
+          <t>246056.SH</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>1.01Y</t>
+          <t>2.08Y</t>
         </is>
       </c>
       <c r="E65" s="4" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="F65" s="3"/>
+        <v>8.0</v>
+      </c>
+      <c r="F65" s="4" t="n">
+        <v>6.0</v>
+      </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
-        </is>
-      </c>
-      <c r="H65" s="3"/>
-      <c r="I65" s="3"/>
+          <t>1.40 ~ 1.90</t>
+        </is>
+      </c>
+      <c r="H65" s="4" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="I65" s="4" t="n">
+        <v>41.43</v>
+      </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="K65" s="3" t="inlineStr">
+        <is>
+          <t>25恒信Z1</t>
+        </is>
+      </c>
+      <c r="L65" s="3" t="inlineStr">
+        <is>
+          <t>2.16Y+2.00Y</t>
+        </is>
+      </c>
+      <c r="M65" s="3" t="inlineStr">
+        <is>
+          <t>1.7153</t>
+        </is>
+      </c>
+      <c r="N65" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O65" s="3" t="inlineStr">
+        <is>
+          <t>海通恒信国际融资租赁股份有限公司</t>
+        </is>
+      </c>
+      <c r="P65" s="3" t="inlineStr">
+        <is>
+          <t>C- 24.06</t>
+        </is>
+      </c>
+      <c r="Q65" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="R65" s="3" t="inlineStr">
+        <is>
+          <t>09-17 15:00</t>
+        </is>
+      </c>
+      <c r="S65" s="3" t="inlineStr">
+        <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K65" s="3" t="inlineStr">
-        <is>
-          <t>25平安点创MTN003</t>
-        </is>
-      </c>
-      <c r="L65" s="3" t="inlineStr">
-        <is>
-          <t>1.11Y</t>
-        </is>
-      </c>
-      <c r="M65" s="3" t="inlineStr">
-        <is>
-          <t>1.7155</t>
-        </is>
-      </c>
-      <c r="N65" s="3" t="inlineStr">
-        <is>
-          <t>--/1.6500</t>
-        </is>
-      </c>
-      <c r="O65" s="3" t="inlineStr">
-        <is>
-          <t>平安点创国际融资租赁有限公司</t>
-        </is>
-      </c>
-      <c r="P65" s="3" t="inlineStr">
-        <is>
-          <t>C- 11.60</t>
-        </is>
-      </c>
-      <c r="Q65" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="R65" s="3" t="inlineStr">
-        <is>
-          <t>09-17 15:00</t>
-        </is>
-      </c>
-      <c r="S65" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T65" s="3" t="inlineStr">
         <is>
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="U65" s="3"/>
+      <c r="U65" s="4" t="n">
+        <v>3.1</v>
+      </c>
       <c r="V65" s="3"/>
       <c r="W65" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X65" s="3" t="inlineStr">
         <is>
-          <t>1.76%~1.86%</t>
+          <t>1.64%~1.74%</t>
         </is>
       </c>
       <c r="Y65" s="3" t="inlineStr">
@@ -15213,11 +15221,7 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z65" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z65" s="3"/>
       <c r="AA65" s="3" t="inlineStr">
         <is>
           <t>上海市</t>
@@ -15225,12 +15229,12 @@
       </c>
       <c r="AB65" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟将不低于70%的部分用于支持中小微企业发展,具体方式为向中小微企业投放保理款(含置换3个月内投放或新增投放),剩余部分用于偿还有息负债。</t>
+          <t>本期公司债券募集资金拟用于置换发行人通过自有资金偿还的公司债券本金[23恒信G2]</t>
         </is>
       </c>
       <c r="AC65" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,中信证券股份有限公司</t>
+          <t>国泰海通证券股份有限公司,华泰联合证券有限责任公司</t>
         </is>
       </c>
       <c r="AD65" s="3"/>
@@ -15241,7 +15245,7 @@
       </c>
       <c r="AF65" s="3" t="inlineStr">
         <is>
-          <t>外商独资企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG65" s="3" t="inlineStr">
@@ -15251,22 +15255,22 @@
       </c>
       <c r="AH65" s="3" t="inlineStr">
         <is>
-          <t>平安点创国际融资租赁有限公司2026年面向专业投资者非公开发行中小微企业支持公司债券(第一期)(品种一)(取消发行)</t>
+          <t>海通恒信国际融资租赁股份有限公司2026年面向专业投资者公开发行公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI65" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ65" s="3" t="inlineStr">
         <is>
-          <t>2027-09-26</t>
+          <t>2028-10-21</t>
         </is>
       </c>
       <c r="AK65" s="3" t="inlineStr">
         <is>
-          <t>休1</t>
+          <t>休2</t>
         </is>
       </c>
       <c r="AL65" s="3" t="inlineStr">
@@ -15276,7 +15280,7 @@
       </c>
       <c r="AM65" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AN65" s="3" t="inlineStr">
@@ -15344,59 +15348,59 @@
     <row r="66" customHeight="true" ht="18.0">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>26恒信G3</t>
+          <t>26正泰MTN002(科创债)</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>09-17 19:00</t>
+          <t>09-17 18:00</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>246056.SH</t>
+          <t>102683707.IB</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>2.08Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E66" s="4" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 1.90</t>
+          <t>1.70 ~ 2.15</t>
         </is>
       </c>
       <c r="H66" s="4" t="n">
-        <v>1.67</v>
+        <v>1.96</v>
       </c>
       <c r="I66" s="4" t="n">
-        <v>41.43</v>
+        <v>70.21</v>
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="K66" s="3" t="inlineStr">
         <is>
-          <t>25恒信Z1</t>
+          <t>26正泰MTN001(科创债)</t>
         </is>
       </c>
       <c r="L66" s="3" t="inlineStr">
         <is>
-          <t>2.16Y+2.00Y</t>
+          <t>2.54Y</t>
         </is>
       </c>
       <c r="M66" s="3" t="inlineStr">
         <is>
-          <t>1.7153</t>
+          <t>1.9670</t>
         </is>
       </c>
       <c r="N66" s="3" t="inlineStr">
@@ -15406,12 +15410,12 @@
       </c>
       <c r="O66" s="3" t="inlineStr">
         <is>
-          <t>海通恒信国际融资租赁股份有限公司</t>
+          <t>正泰集团股份有限公司</t>
         </is>
       </c>
       <c r="P66" s="3" t="inlineStr">
         <is>
-          <t>C- 24.06</t>
+          <t>C+ 34.29</t>
         </is>
       </c>
       <c r="Q66" s="3" t="inlineStr">
@@ -15421,7 +15425,7 @@
       </c>
       <c r="R66" s="3" t="inlineStr">
         <is>
-          <t>09-17 15:00</t>
+          <t>09-17 09:00</t>
         </is>
       </c>
       <c r="S66" s="3" t="inlineStr">
@@ -15431,63 +15435,65 @@
       </c>
       <c r="T66" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="U66" s="4" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="V66" s="3"/>
+        <v>1.38</v>
+      </c>
+      <c r="V66" s="4" t="n">
+        <v>1.5</v>
+      </c>
       <c r="W66" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X66" s="3" t="inlineStr">
         <is>
-          <t>1.64%~1.74%</t>
+          <t>1.92%~2.02%</t>
         </is>
       </c>
       <c r="Y66" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z66" s="3"/>
       <c r="AA66" s="3" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>浙江省-温州市</t>
         </is>
       </c>
       <c r="AB66" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金拟用于置换发行人通过自有资金偿还的公司债券本金[23恒信G2]</t>
+          <t>发行人本次拟发行科技创新债券金额5亿元，全部募集资金用于拟归还一年内到期有息借款，最终用于发行人科技创新及主营业务生产经营，主要投向研发设备购置、核心生产装备升级改造、关键技术配套原材料及核心物料采购等领域</t>
         </is>
       </c>
       <c r="AC66" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,华泰联合证券有限责任公司</t>
+          <t>浙商银行股份有限公司,中国建设银行股份有限公司</t>
         </is>
       </c>
       <c r="AD66" s="3"/>
       <c r="AE66" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF66" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>民营企业</t>
         </is>
       </c>
       <c r="AG66" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH66" s="3" t="inlineStr">
         <is>
-          <t>海通恒信国际融资租赁股份有限公司2026年面向专业投资者公开发行公司债券(第三期)</t>
+          <t>正泰集团股份有限公司2026年度第二期科技创新债券</t>
         </is>
       </c>
       <c r="AI66" s="3" t="inlineStr">
@@ -15497,57 +15503,53 @@
       </c>
       <c r="AJ66" s="3" t="inlineStr">
         <is>
-          <t>2028-10-21</t>
-        </is>
-      </c>
-      <c r="AK66" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2029-09-18</t>
+        </is>
+      </c>
+      <c r="AK66" s="3"/>
       <c r="AL66" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="AM66" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AN66" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="AO66" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP66" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ66" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>电力设备制造</t>
         </is>
       </c>
       <c r="AR66" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>电网设备</t>
         </is>
       </c>
       <c r="AS66" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>电网设备</t>
         </is>
       </c>
       <c r="AT66" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>高低压设备</t>
         </is>
       </c>
       <c r="AU66" s="3" t="inlineStr">
@@ -15580,7 +15582,7 @@
     <row r="67" customHeight="true" ht="18.0">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>26正泰MTN002(科创债)</t>
+          <t>26济南高新MTN008B</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -15590,64 +15592,64 @@
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>102683707.IB</t>
+          <t>102683699.IB</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>10Y</t>
         </is>
       </c>
       <c r="E67" s="4" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>5.0</v>
+        <v>2.5</v>
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.15</t>
+          <t>2.20 ~ 3.20</t>
         </is>
       </c>
       <c r="H67" s="4" t="n">
-        <v>1.96</v>
+        <v>2.63</v>
       </c>
       <c r="I67" s="4" t="n">
-        <v>70.21</v>
+        <v>94.38</v>
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>26正泰MTN001(科创债)</t>
+          <t>26济南高新MTN005B</t>
         </is>
       </c>
       <c r="L67" s="3" t="inlineStr">
         <is>
-          <t>2.54Y</t>
+          <t>9.81Y</t>
         </is>
       </c>
       <c r="M67" s="3" t="inlineStr">
         <is>
-          <t>1.9670</t>
+          <t>2.6351</t>
         </is>
       </c>
       <c r="N67" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/2.5900</t>
         </is>
       </c>
       <c r="O67" s="3" t="inlineStr">
         <is>
-          <t>正泰集团股份有限公司</t>
+          <t>济南高新控股集团有限公司</t>
         </is>
       </c>
       <c r="P67" s="3" t="inlineStr">
         <is>
-          <t>C+ 34.29</t>
+          <t>C+ 31.02</t>
         </is>
       </c>
       <c r="Q67" s="3" t="inlineStr">
@@ -15671,40 +15673,44 @@
         </is>
       </c>
       <c r="U67" s="4" t="n">
-        <v>1.38</v>
+        <v>4.8</v>
       </c>
       <c r="V67" s="4" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="W67" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X67" s="3" t="inlineStr">
         <is>
-          <t>1.92%~2.02%</t>
+          <t>2.44%~2.54%</t>
         </is>
       </c>
       <c r="Y67" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z67" s="3"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z67" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA67" s="3" t="inlineStr">
         <is>
-          <t>浙江省-温州市</t>
+          <t>山东省-济南市</t>
         </is>
       </c>
       <c r="AB67" s="3" t="inlineStr">
         <is>
-          <t>发行人本次拟发行科技创新债券金额5亿元，全部募集资金用于拟归还一年内到期有息借款，最终用于发行人科技创新及主营业务生产经营，主要投向研发设备购置、核心生产装备升级改造、关键技术配套原材料及核心物料采购等领域</t>
+          <t>发行人本期中期票据基础发行金额为人民币0亿元，发行金额上限为人民币6.5亿元，所募集的资金拟用于偿还发行人即将到期的债务融资工具[26济南高新SCP001]</t>
         </is>
       </c>
       <c r="AC67" s="3" t="inlineStr">
         <is>
-          <t>浙商银行股份有限公司,中国建设银行股份有限公司</t>
+          <t>中国农业银行股份有限公司,中国银行股份有限公司</t>
         </is>
       </c>
       <c r="AD67" s="3"/>
@@ -15715,7 +15721,7 @@
       </c>
       <c r="AF67" s="3" t="inlineStr">
         <is>
-          <t>民营企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG67" s="3" t="inlineStr">
@@ -15725,7 +15731,7 @@
       </c>
       <c r="AH67" s="3" t="inlineStr">
         <is>
-          <t>正泰集团股份有限公司2026年度第二期科技创新债券</t>
+          <t>济南高新控股集团有限公司2026年度第八期中期票据(品种二)</t>
         </is>
       </c>
       <c r="AI67" s="3" t="inlineStr">
@@ -15735,7 +15741,7 @@
       </c>
       <c r="AJ67" s="3" t="inlineStr">
         <is>
-          <t>2029-09-18</t>
+          <t>2036-09-18</t>
         </is>
       </c>
       <c r="AK67" s="3"/>
@@ -15761,27 +15767,27 @@
       </c>
       <c r="AP67" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ67" s="3" t="inlineStr">
         <is>
-          <t>电力设备制造</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR67" s="3" t="inlineStr">
         <is>
-          <t>电网设备</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS67" s="3" t="inlineStr">
         <is>
-          <t>电网设备</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT67" s="3" t="inlineStr">
         <is>
-          <t>高低压设备</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU67" s="3" t="inlineStr">
@@ -15814,7 +15820,7 @@
     <row r="68" customHeight="true" ht="18.0">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>26济南高新MTN008B</t>
+          <t>26济南高新MTN008A</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -15824,54 +15830,54 @@
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>102683699.IB</t>
+          <t>102683698.IB</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>10Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E68" s="4" t="n">
-        <v>3.0</v>
+        <v>3.5</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>2.5</v>
+        <v>4.0</v>
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2.20 ~ 3.20</t>
+          <t>1.40 ~ 2.40</t>
         </is>
       </c>
       <c r="H68" s="4" t="n">
-        <v>2.63</v>
+        <v>1.89</v>
       </c>
       <c r="I68" s="4" t="n">
-        <v>94.38</v>
+        <v>47.94</v>
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="K68" s="3" t="inlineStr">
         <is>
-          <t>26济南高新MTN005B</t>
+          <t>26济南高新MTN006A</t>
         </is>
       </c>
       <c r="L68" s="3" t="inlineStr">
         <is>
-          <t>9.81Y</t>
+          <t>4.82Y</t>
         </is>
       </c>
       <c r="M68" s="3" t="inlineStr">
         <is>
-          <t>2.6351</t>
+          <t>1.9150</t>
         </is>
       </c>
       <c r="N68" s="3" t="inlineStr">
         <is>
-          <t>--/2.5900</t>
+          <t>1.9200/--</t>
         </is>
       </c>
       <c r="O68" s="3" t="inlineStr">
@@ -15908,7 +15914,7 @@
         <v>4.8</v>
       </c>
       <c r="V68" s="4" t="n">
-        <v>1.2</v>
+        <v>5.33</v>
       </c>
       <c r="W68" s="3" t="inlineStr">
         <is>
@@ -15917,7 +15923,7 @@
       </c>
       <c r="X68" s="3" t="inlineStr">
         <is>
-          <t>2.44%~2.54%</t>
+          <t>1.90%~2.00%</t>
         </is>
       </c>
       <c r="Y68" s="3" t="inlineStr">
@@ -15963,7 +15969,7 @@
       </c>
       <c r="AH68" s="3" t="inlineStr">
         <is>
-          <t>济南高新控股集团有限公司2026年度第八期中期票据(品种二)</t>
+          <t>济南高新控股集团有限公司2026年度第八期中期票据(品种一)</t>
         </is>
       </c>
       <c r="AI68" s="3" t="inlineStr">
@@ -15973,7 +15979,7 @@
       </c>
       <c r="AJ68" s="3" t="inlineStr">
         <is>
-          <t>2036-09-18</t>
+          <t>2031-09-18</t>
         </is>
       </c>
       <c r="AK68" s="3"/>
@@ -16052,7 +16058,7 @@
     <row r="69" customHeight="true" ht="18.0">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>26济南高新MTN008A</t>
+          <t>26广东农垦SCP006</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -16062,92 +16068,92 @@
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>102683698.IB</t>
+          <t>012682289.IB</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>0.73Y</t>
         </is>
       </c>
       <c r="E69" s="4" t="n">
-        <v>3.5</v>
+        <v>5.0</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
+          <t>1.30 ~ 1.60</t>
         </is>
       </c>
       <c r="H69" s="4" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="I69" s="4" t="n">
+        <v>18.33</v>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="K69" s="3" t="inlineStr">
+        <is>
+          <t>26广东农垦SCP005</t>
+        </is>
+      </c>
+      <c r="L69" s="3" t="inlineStr">
+        <is>
+          <t>239D</t>
+        </is>
+      </c>
+      <c r="M69" s="3" t="inlineStr">
+        <is>
+          <t>1.5308</t>
+        </is>
+      </c>
+      <c r="N69" s="3" t="inlineStr">
+        <is>
+          <t>1.5400/--</t>
+        </is>
+      </c>
+      <c r="O69" s="3" t="inlineStr">
+        <is>
+          <t>广东省农垦集团公司</t>
+        </is>
+      </c>
+      <c r="P69" s="3" t="inlineStr">
+        <is>
+          <t>B- 40.09</t>
+        </is>
+      </c>
+      <c r="Q69" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="R69" s="3" t="inlineStr">
+        <is>
+          <t>09-17 09:00</t>
+        </is>
+      </c>
+      <c r="S69" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="T69" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="U69" s="4" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="V69" s="4" t="n">
         <v>1.89</v>
       </c>
-      <c r="I69" s="4" t="n">
-        <v>47.94</v>
-      </c>
-      <c r="J69" s="3" t="inlineStr">
-        <is>
-          <t>1.91</t>
-        </is>
-      </c>
-      <c r="K69" s="3" t="inlineStr">
-        <is>
-          <t>26济南高新MTN006A</t>
-        </is>
-      </c>
-      <c r="L69" s="3" t="inlineStr">
-        <is>
-          <t>4.82Y</t>
-        </is>
-      </c>
-      <c r="M69" s="3" t="inlineStr">
-        <is>
-          <t>1.9150</t>
-        </is>
-      </c>
-      <c r="N69" s="3" t="inlineStr">
-        <is>
-          <t>1.9200/--</t>
-        </is>
-      </c>
-      <c r="O69" s="3" t="inlineStr">
-        <is>
-          <t>济南高新控股集团有限公司</t>
-        </is>
-      </c>
-      <c r="P69" s="3" t="inlineStr">
-        <is>
-          <t>C+ 31.02</t>
-        </is>
-      </c>
-      <c r="Q69" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="R69" s="3" t="inlineStr">
-        <is>
-          <t>09-17 09:00</t>
-        </is>
-      </c>
-      <c r="S69" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="T69" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="U69" s="4" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="V69" s="4" t="n">
-        <v>5.33</v>
-      </c>
       <c r="W69" s="3" t="inlineStr">
         <is>
           <t>5+</t>
@@ -16155,7 +16161,7 @@
       </c>
       <c r="X69" s="3" t="inlineStr">
         <is>
-          <t>1.90%~2.00%</t>
+          <t>1.53%~1.57%</t>
         </is>
       </c>
       <c r="Y69" s="3" t="inlineStr">
@@ -16163,30 +16169,26 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z69" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z69" s="3"/>
       <c r="AA69" s="3" t="inlineStr">
         <is>
-          <t>山东省-济南市</t>
+          <t>广东省-广州市</t>
         </is>
       </c>
       <c r="AB69" s="3" t="inlineStr">
         <is>
-          <t>发行人本期中期票据基础发行金额为人民币0亿元，发行金额上限为人民币6.5亿元，所募集的资金拟用于偿还发行人即将到期的债务融资工具[26济南高新SCP001]</t>
+          <t>发行人本期超短期融资券发行金额为5亿元,期限为267天,拟用于偿还发行人到期债务融资工具[26广东农垦SCP002]</t>
         </is>
       </c>
       <c r="AC69" s="3" t="inlineStr">
         <is>
-          <t>中国农业银行股份有限公司,中国银行股份有限公司</t>
+          <t>浙商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD69" s="3"/>
       <c r="AE69" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF69" s="3" t="inlineStr">
@@ -16201,7 +16203,7 @@
       </c>
       <c r="AH69" s="3" t="inlineStr">
         <is>
-          <t>济南高新控股集团有限公司2026年度第八期中期票据(品种一)</t>
+          <t>广东省农垦集团公司2026年度第六期超短期融资券</t>
         </is>
       </c>
       <c r="AI69" s="3" t="inlineStr">
@@ -16211,10 +16213,14 @@
       </c>
       <c r="AJ69" s="3" t="inlineStr">
         <is>
-          <t>2031-09-18</t>
-        </is>
-      </c>
-      <c r="AK69" s="3"/>
+          <t>2027-06-12</t>
+        </is>
+      </c>
+      <c r="AK69" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL69" s="3" t="inlineStr">
         <is>
           <t>2026-09-20</t>
@@ -16237,27 +16243,27 @@
       </c>
       <c r="AP69" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ69" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>农林牧渔</t>
         </is>
       </c>
       <c r="AR69" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>综合农林牧渔</t>
         </is>
       </c>
       <c r="AS69" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>综合农林牧渔</t>
         </is>
       </c>
       <c r="AT69" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU69" s="3" t="inlineStr">
@@ -16290,74 +16296,74 @@
     <row r="70" customHeight="true" ht="18.0">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>26广东农垦SCP006</t>
+          <t>26临空K1</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>09-17 18:00</t>
+          <t>09-17 19:00</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>012682289.IB</t>
+          <t>283990.SH</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>0.73Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E70" s="4" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.60</t>
+          <t>1.50 ~ 2.30</t>
         </is>
       </c>
       <c r="H70" s="4" t="n">
-        <v>1.39</v>
+        <v>1.67</v>
       </c>
       <c r="I70" s="4" t="n">
-        <v>18.33</v>
+        <v>25.94</v>
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="K70" s="3" t="inlineStr">
         <is>
-          <t>26广东农垦SCP005</t>
+          <t>24策源K1</t>
         </is>
       </c>
       <c r="L70" s="3" t="inlineStr">
         <is>
-          <t>239D</t>
+          <t>2.99Y</t>
         </is>
       </c>
       <c r="M70" s="3" t="inlineStr">
         <is>
-          <t>1.5308</t>
+          <t>2.0295</t>
         </is>
       </c>
       <c r="N70" s="3" t="inlineStr">
         <is>
-          <t>1.5400/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O70" s="3" t="inlineStr">
         <is>
-          <t>广东省农垦集团公司</t>
+          <t>杭州临空控股发展有限公司</t>
         </is>
       </c>
       <c r="P70" s="3" t="inlineStr">
         <is>
-          <t>B- 40.09</t>
+          <t>E 0.00</t>
         </is>
       </c>
       <c r="Q70" s="3" t="inlineStr">
@@ -16367,7 +16373,7 @@
       </c>
       <c r="R70" s="3" t="inlineStr">
         <is>
-          <t>09-17 09:00</t>
+          <t>09-17 15:00</t>
         </is>
       </c>
       <c r="S70" s="3" t="inlineStr">
@@ -16381,46 +16387,48 @@
         </is>
       </c>
       <c r="U70" s="4" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="V70" s="4" t="n">
-        <v>1.89</v>
-      </c>
+        <v>3.31</v>
+      </c>
+      <c r="V70" s="3"/>
       <c r="W70" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X70" s="3" t="inlineStr">
         <is>
-          <t>1.53%~1.57%</t>
+          <t>1.99%~2.09%</t>
         </is>
       </c>
       <c r="Y70" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z70" s="3"/>
       <c r="AA70" s="3" t="inlineStr">
         <is>
-          <t>广东省-广州市</t>
+          <t>浙江省-杭州市</t>
         </is>
       </c>
       <c r="AB70" s="3" t="inlineStr">
         <is>
-          <t>发行人本期超短期融资券发行金额为5亿元,期限为267天,拟用于偿还发行人到期债务融资工具[26广东农垦SCP002]</t>
+          <t>本期债券的发行总额为不超过2亿元(含2亿元),扣除发行费用后,拟不低于70%用于投向科技创新领域,包括但不限于:直接对具有科技创新属性的公司开展股权投资;向创业投资基金、政府出资产业基金等进行出资;置换发行前12个月内上述科技创新领域的相关投资支出;以及其他符合国家产业政策的科技创新领域用途。本期债券募集资金剩余部分用于补充流动资金。</t>
         </is>
       </c>
       <c r="AC70" s="3" t="inlineStr">
         <is>
-          <t>浙商银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD70" s="3"/>
+          <t>国金证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD70" s="3" t="inlineStr">
+        <is>
+          <t>杭州萧山国有资本运营集团有限公司</t>
+        </is>
+      </c>
       <c r="AE70" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF70" s="3" t="inlineStr">
@@ -16430,37 +16438,33 @@
       </c>
       <c r="AG70" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH70" s="3" t="inlineStr">
         <is>
-          <t>广东省农垦集团公司2026年度第六期超短期融资券</t>
+          <t>杭州临空控股发展有限公司2026年面向专业投资者非公开发行科技创新公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI70" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ70" s="3" t="inlineStr">
         <is>
-          <t>2027-06-12</t>
-        </is>
-      </c>
-      <c r="AK70" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2031-09-18</t>
+        </is>
+      </c>
+      <c r="AK70" s="3"/>
       <c r="AL70" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AM70" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AN70" s="3" t="inlineStr">
@@ -16470,27 +16474,23 @@
       </c>
       <c r="AO70" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP70" s="3" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP70" s="3"/>
       <c r="AQ70" s="3" t="inlineStr">
         <is>
-          <t>农林牧渔</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR70" s="3" t="inlineStr">
         <is>
-          <t>综合农林牧渔</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AS70" s="3" t="inlineStr">
         <is>
-          <t>综合农林牧渔</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AT70" s="3" t="inlineStr">
@@ -16500,17 +16500,17 @@
       </c>
       <c r="AU70" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-09-18</t>
         </is>
       </c>
       <c r="AV70" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW70" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX70" s="3" t="inlineStr">
@@ -16528,7 +16528,7 @@
     <row r="71" customHeight="true" ht="18.0">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>26临空K1</t>
+          <t>26山钢Y8</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -16538,49 +16538,49 @@
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>283990.SH</t>
+          <t>284068.SH</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E71" s="4" t="n">
-        <v>2.0</v>
+        <v>10.0</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>2.0</v>
+        <v>10.0</v>
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.30</t>
+          <t>1.70 ~ 2.30</t>
         </is>
       </c>
       <c r="H71" s="4" t="n">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="I71" s="4" t="n">
-        <v>25.94</v>
+        <v>69.21</v>
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="K71" s="3" t="inlineStr">
         <is>
-          <t>24策源K1</t>
+          <t>26山钢Y7</t>
         </is>
       </c>
       <c r="L71" s="3" t="inlineStr">
         <is>
-          <t>2.99Y</t>
+          <t>2.97Y+N</t>
         </is>
       </c>
       <c r="M71" s="3" t="inlineStr">
         <is>
-          <t>2.0295</t>
+          <t>1.9964</t>
         </is>
       </c>
       <c r="N71" s="3" t="inlineStr">
@@ -16590,12 +16590,12 @@
       </c>
       <c r="O71" s="3" t="inlineStr">
         <is>
-          <t>杭州临空控股发展有限公司</t>
+          <t>山东钢铁集团有限公司</t>
         </is>
       </c>
       <c r="P71" s="3" t="inlineStr">
         <is>
-          <t>E 0.00</t>
+          <t>C 29.89</t>
         </is>
       </c>
       <c r="Q71" s="3" t="inlineStr">
@@ -16619,45 +16619,41 @@
         </is>
       </c>
       <c r="U71" s="4" t="n">
-        <v>3.31</v>
+        <v>1.83</v>
       </c>
       <c r="V71" s="3"/>
       <c r="W71" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X71" s="3" t="inlineStr">
         <is>
-          <t>1.99%~2.09%</t>
+          <t>1.91%~2.01%</t>
         </is>
       </c>
       <c r="Y71" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z71" s="3"/>
       <c r="AA71" s="3" t="inlineStr">
         <is>
-          <t>浙江省-杭州市</t>
+          <t>山东省-济南市</t>
         </is>
       </c>
       <c r="AB71" s="3" t="inlineStr">
         <is>
-          <t>本期债券的发行总额为不超过2亿元(含2亿元),扣除发行费用后,拟不低于70%用于投向科技创新领域,包括但不限于:直接对具有科技创新属性的公司开展股权投资;向创业投资基金、政府出资产业基金等进行出资;置换发行前12个月内上述科技创新领域的相关投资支出;以及其他符合国家产业政策的科技创新领域用途。本期债券募集资金剩余部分用于补充流动资金。</t>
+          <t>本期债券的募集资金在扣除发行费用后,拟将用于置换到期的公司债券本金[24山钢Y3]</t>
         </is>
       </c>
       <c r="AC71" s="3" t="inlineStr">
         <is>
-          <t>国金证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD71" s="3" t="inlineStr">
-        <is>
-          <t>杭州萧山国有资本运营集团有限公司</t>
-        </is>
-      </c>
+          <t>国泰海通证券股份有限公司,华泰联合证券有限责任公司,中国国际金融股份有限公司,中信证券股份有限公司,中信建投证券股份有限公司,招商证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD71" s="3"/>
       <c r="AE71" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -16675,7 +16671,7 @@
       </c>
       <c r="AH71" s="3" t="inlineStr">
         <is>
-          <t>杭州临空控股发展有限公司2026年面向专业投资者非公开发行科技创新公司债券(第一期)</t>
+          <t>山东钢铁集团有限公司2026年面向专业投资者非公开发行可续期公司债券(第六期)</t>
         </is>
       </c>
       <c r="AI71" s="3" t="inlineStr">
@@ -16685,18 +16681,18 @@
       </c>
       <c r="AJ71" s="3" t="inlineStr">
         <is>
-          <t>2031-09-18</t>
+          <t>2029-09-18</t>
         </is>
       </c>
       <c r="AK71" s="3"/>
       <c r="AL71" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t/>
         </is>
       </c>
       <c r="AM71" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AN71" s="3" t="inlineStr">
@@ -16706,48 +16702,52 @@
       </c>
       <c r="AO71" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP71" s="3"/>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP71" s="3" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
       <c r="AQ71" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>金属和非金属矿产</t>
         </is>
       </c>
       <c r="AR71" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>钢铁</t>
         </is>
       </c>
       <c r="AS71" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>普钢</t>
         </is>
       </c>
       <c r="AT71" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>钢铁</t>
         </is>
       </c>
       <c r="AU71" s="3" t="inlineStr">
         <is>
-          <t>2029-09-18</t>
+          <t/>
         </is>
       </c>
       <c r="AV71" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW71" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX71" s="3" t="inlineStr">
         <is>
-          <t>普通债权</t>
+          <t>次级债权</t>
         </is>
       </c>
       <c r="AY71" s="3" t="inlineStr">
@@ -16760,74 +16760,74 @@
     <row r="72" customHeight="true" ht="18.0">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>26山钢Y8</t>
+          <t>26伊宁国资MTN001</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>09-17 19:00</t>
+          <t>09-17 18:00</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>284068.SH</t>
+          <t>102683712.IB</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E72" s="4" t="n">
-        <v>10.0</v>
+        <v>4.2</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>10.0</v>
+        <v>4.2</v>
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.30</t>
+          <t>1.90 ~ 2.70</t>
         </is>
       </c>
       <c r="H72" s="4" t="n">
-        <v>1.95</v>
+        <v>2.18</v>
       </c>
       <c r="I72" s="4" t="n">
-        <v>69.21</v>
+        <v>76.94</v>
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="K72" s="3" t="inlineStr">
         <is>
-          <t>26山钢Y7</t>
+          <t>25伊宁国资MTN001</t>
         </is>
       </c>
       <c r="L72" s="3" t="inlineStr">
         <is>
-          <t>2.97Y+N</t>
+          <t>1.31Y</t>
         </is>
       </c>
       <c r="M72" s="3" t="inlineStr">
         <is>
-          <t>1.9964</t>
+          <t>1.6543</t>
         </is>
       </c>
       <c r="N72" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.6500</t>
         </is>
       </c>
       <c r="O72" s="3" t="inlineStr">
         <is>
-          <t>山东钢铁集团有限公司</t>
+          <t>伊宁市国有资产投资经营(集团)有限责任公司</t>
         </is>
       </c>
       <c r="P72" s="3" t="inlineStr">
         <is>
-          <t>C 29.89</t>
+          <t>C 27.57</t>
         </is>
       </c>
       <c r="Q72" s="3" t="inlineStr">
@@ -16837,7 +16837,7 @@
       </c>
       <c r="R72" s="3" t="inlineStr">
         <is>
-          <t>09-17 15:00</t>
+          <t>09-17 09:00</t>
         </is>
       </c>
       <c r="S72" s="3" t="inlineStr">
@@ -16851,44 +16851,46 @@
         </is>
       </c>
       <c r="U72" s="4" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="V72" s="3"/>
+        <v>2.3333</v>
+      </c>
+      <c r="V72" s="4" t="n">
+        <v>1.2</v>
+      </c>
       <c r="W72" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X72" s="3" t="inlineStr">
         <is>
-          <t>1.91%~2.01%</t>
+          <t>1.96%~2.06%</t>
         </is>
       </c>
       <c r="Y72" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z72" s="3"/>
       <c r="AA72" s="3" t="inlineStr">
         <is>
-          <t>山东省-济南市</t>
+          <t>新疆维吾尔自治区-伊犁哈萨克自治州</t>
         </is>
       </c>
       <c r="AB72" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金在扣除发行费用后,拟将用于置换到期的公司债券本金[24山钢Y3]</t>
+          <t>首期发行金额4.20亿元，募集资金扣除发行费用后，用于偿还发行人存量债务融资工具本金[24伊宁国资MTN002,24伊宁国资MTN001,24伊宁国资MTN003,25伊宁国资MTN001]</t>
         </is>
       </c>
       <c r="AC72" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,华泰联合证券有限责任公司,中国国际金融股份有限公司,中信证券股份有限公司,中信建投证券股份有限公司,招商证券股份有限公司</t>
+          <t>中信银行股份有限公司,光大证券股份有限公司</t>
         </is>
       </c>
       <c r="AD72" s="3"/>
       <c r="AE72" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF72" s="3" t="inlineStr">
@@ -16898,75 +16900,75 @@
       </c>
       <c r="AG72" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH72" s="3" t="inlineStr">
         <is>
-          <t>山东钢铁集团有限公司2026年面向专业投资者非公开发行可续期公司债券(第六期)</t>
+          <t>伊宁市国有资产投资经营(集团)有限责任公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI72" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ72" s="3" t="inlineStr">
         <is>
-          <t>2029-09-18</t>
+          <t>2031-09-18</t>
         </is>
       </c>
       <c r="AK72" s="3"/>
       <c r="AL72" s="3" t="inlineStr">
         <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="AM72" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AN72" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="AO72" s="3" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP72" s="3" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="AQ72" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AR72" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AS72" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AT72" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU72" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM72" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="AN72" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="AO72" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP72" s="3" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
-      <c r="AQ72" s="3" t="inlineStr">
-        <is>
-          <t>金属和非金属矿产</t>
-        </is>
-      </c>
-      <c r="AR72" s="3" t="inlineStr">
-        <is>
-          <t>钢铁</t>
-        </is>
-      </c>
-      <c r="AS72" s="3" t="inlineStr">
-        <is>
-          <t>普钢</t>
-        </is>
-      </c>
-      <c r="AT72" s="3" t="inlineStr">
-        <is>
-          <t>钢铁</t>
-        </is>
-      </c>
-      <c r="AU72" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV72" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -16974,12 +16976,12 @@
       </c>
       <c r="AW72" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX72" s="3" t="inlineStr">
         <is>
-          <t>次级债权</t>
+          <t>普通债权</t>
         </is>
       </c>
       <c r="AY72" s="3" t="inlineStr">
@@ -16987,79 +16989,81 @@
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="AZ72" s="3"/>
+      <c r="AZ72" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="73" customHeight="true" ht="18.0">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>26伊宁国资MTN001</t>
+          <t>26万集K1</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>09-17 18:00</t>
+          <t>09-17 19:00</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>102683712.IB</t>
+          <t>520492.SZ</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E73" s="4" t="n">
-        <v>4.2</v>
+        <v>5.0</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>4.2</v>
+        <v>2.83</v>
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>1.90 ~ 2.70</t>
+          <t>4.00 ~ 5.00</t>
         </is>
       </c>
       <c r="H73" s="4" t="n">
-        <v>2.18</v>
+        <v>4.9</v>
       </c>
       <c r="I73" s="4" t="n">
-        <v>76.94</v>
+        <v>364.21</v>
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="K73" s="3" t="inlineStr">
         <is>
-          <t>25伊宁国资MTN001</t>
+          <t>24盐国05</t>
         </is>
       </c>
       <c r="L73" s="3" t="inlineStr">
         <is>
-          <t>1.31Y</t>
+          <t>3.00Y</t>
         </is>
       </c>
       <c r="M73" s="3" t="inlineStr">
         <is>
-          <t>1.6543</t>
+          <t>1.9055</t>
         </is>
       </c>
       <c r="N73" s="3" t="inlineStr">
         <is>
-          <t>--/1.6500</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O73" s="3" t="inlineStr">
         <is>
-          <t>伊宁市国有资产投资经营(集团)有限责任公司</t>
+          <t>万达集团股份有限公司</t>
         </is>
       </c>
       <c r="P73" s="3" t="inlineStr">
         <is>
-          <t>C 27.57</t>
+          <t>E 0.00</t>
         </is>
       </c>
       <c r="Q73" s="3" t="inlineStr">
@@ -17069,7 +17073,7 @@
       </c>
       <c r="R73" s="3" t="inlineStr">
         <is>
-          <t>09-17 09:00</t>
+          <t>09-17 15:00</t>
         </is>
       </c>
       <c r="S73" s="3" t="inlineStr">
@@ -17083,77 +17087,75 @@
         </is>
       </c>
       <c r="U73" s="4" t="n">
-        <v>2.3333</v>
-      </c>
-      <c r="V73" s="4" t="n">
-        <v>1.2</v>
-      </c>
+        <v>1.0</v>
+      </c>
+      <c r="V73" s="3"/>
       <c r="W73" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>7-</t>
         </is>
       </c>
       <c r="X73" s="3" t="inlineStr">
         <is>
-          <t>1.96%~2.06%</t>
+          <t>4.50%~4.60%</t>
         </is>
       </c>
       <c r="Y73" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z73" s="3"/>
       <c r="AA73" s="3" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区-伊犁哈萨克自治州</t>
+          <t>山东省-东营市</t>
         </is>
       </c>
       <c r="AB73" s="3" t="inlineStr">
         <is>
-          <t>首期发行金额4.20亿元，募集资金扣除发行费用后，用于偿还发行人存量债务融资工具本金[24伊宁国资MTN002,24伊宁国资MTN001,24伊宁国资MTN003,25伊宁国资MTN001]</t>
+          <t>本期债券发行总额不超过5亿元(含5亿元)，募集资金扣除发行费用后，拟全部用于偿还有息债务</t>
         </is>
       </c>
       <c r="AC73" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,光大证券股份有限公司</t>
+          <t>麦高证券有限责任公司</t>
         </is>
       </c>
       <c r="AD73" s="3"/>
       <c r="AE73" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF73" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>民营企业</t>
         </is>
       </c>
       <c r="AG73" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH73" s="3" t="inlineStr">
         <is>
-          <t>伊宁市国有资产投资经营(集团)有限责任公司2026年度第一期中期票据</t>
+          <t>万达集团股份有限公司2026年面向专业投资者非公开发行科技创新公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI73" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ73" s="3" t="inlineStr">
         <is>
-          <t>2031-09-18</t>
+          <t>2029-09-18</t>
         </is>
       </c>
       <c r="AK73" s="3"/>
       <c r="AL73" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t/>
         </is>
       </c>
       <c r="AM73" s="3" t="inlineStr">
@@ -17168,12 +17170,12 @@
       </c>
       <c r="AO73" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP73" s="3" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ73" s="3" t="inlineStr">
@@ -17183,17 +17185,17 @@
       </c>
       <c r="AR73" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>产业集团</t>
         </is>
       </c>
       <c r="AS73" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>产业集团</t>
         </is>
       </c>
       <c r="AT73" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>石油化工</t>
         </is>
       </c>
       <c r="AU73" s="3" t="inlineStr">
@@ -17221,66 +17223,64 @@
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="AZ73" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ73" s="3"/>
     </row>
     <row r="74" customHeight="true" ht="18.0">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>26万集K1</t>
+          <t>26京城建SCP007</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>09-17 19:00</t>
+          <t>09-17 18:00</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>520492.SZ</t>
+          <t>012682291.IB</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.16Y</t>
         </is>
       </c>
       <c r="E74" s="4" t="n">
         <v>5.0</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>2.83</v>
+        <v>5.0</v>
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>4.00 ~ 5.00</t>
+          <t>1.25 ~ 1.50</t>
         </is>
       </c>
       <c r="H74" s="4" t="n">
-        <v>4.9</v>
+        <v>1.31</v>
       </c>
       <c r="I74" s="4" t="n">
-        <v>364.21</v>
+        <v>13.0</v>
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="K74" s="3" t="inlineStr">
         <is>
-          <t>24盐国05</t>
+          <t>26京城建SCP005</t>
         </is>
       </c>
       <c r="L74" s="3" t="inlineStr">
         <is>
-          <t>3.00Y</t>
+          <t>33D</t>
         </is>
       </c>
       <c r="M74" s="3" t="inlineStr">
         <is>
-          <t>1.9055</t>
+          <t>1.4998</t>
         </is>
       </c>
       <c r="N74" s="3" t="inlineStr">
@@ -17290,12 +17290,12 @@
       </c>
       <c r="O74" s="3" t="inlineStr">
         <is>
-          <t>万达集团股份有限公司</t>
+          <t>北京城建集团有限责任公司</t>
         </is>
       </c>
       <c r="P74" s="3" t="inlineStr">
         <is>
-          <t>E 0.00</t>
+          <t>C- 23.27</t>
         </is>
       </c>
       <c r="Q74" s="3" t="inlineStr">
@@ -17305,7 +17305,7 @@
       </c>
       <c r="R74" s="3" t="inlineStr">
         <is>
-          <t>09-17 15:00</t>
+          <t>09-17 09:00</t>
         </is>
       </c>
       <c r="S74" s="3" t="inlineStr">
@@ -17319,122 +17319,124 @@
         </is>
       </c>
       <c r="U74" s="4" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V74" s="4" t="n">
         <v>1.0</v>
       </c>
-      <c r="V74" s="3"/>
       <c r="W74" s="3" t="inlineStr">
         <is>
-          <t>7-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X74" s="3" t="inlineStr">
         <is>
-          <t>4.50%~4.60%</t>
+          <t>1.46%~1.50%</t>
         </is>
       </c>
       <c r="Y74" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z74" s="3"/>
       <c r="AA74" s="3" t="inlineStr">
         <is>
-          <t>山东省-东营市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB74" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行总额不超过5亿元(含5亿元)，募集资金扣除发行费用后，拟全部用于偿还有息债务</t>
+          <t>本期超短期融资券发行金额为5亿元，拟全部用于偿还发行人有息债务。</t>
         </is>
       </c>
       <c r="AC74" s="3" t="inlineStr">
         <is>
-          <t>麦高证券有限责任公司</t>
+          <t>渤海银行股份有限公司,中国民生银行股份有限公司</t>
         </is>
       </c>
       <c r="AD74" s="3"/>
       <c r="AE74" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF74" s="3" t="inlineStr">
         <is>
-          <t>民营企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG74" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH74" s="3" t="inlineStr">
         <is>
-          <t>万达集团股份有限公司2026年面向专业投资者非公开发行科技创新公司债券(第一期)</t>
+          <t>北京城建集团有限责任公司2026年度第七期超短期融资券</t>
         </is>
       </c>
       <c r="AI74" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ74" s="3" t="inlineStr">
         <is>
-          <t>2029-09-18</t>
+          <t>2026-11-17</t>
         </is>
       </c>
       <c r="AK74" s="3"/>
       <c r="AL74" s="3" t="inlineStr">
         <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="AM74" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AN74" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="AO74" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP74" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AQ74" s="3" t="inlineStr">
+        <is>
+          <t>建筑施工</t>
+        </is>
+      </c>
+      <c r="AR74" s="3" t="inlineStr">
+        <is>
+          <t>房屋建筑</t>
+        </is>
+      </c>
+      <c r="AS74" s="3" t="inlineStr">
+        <is>
+          <t>其他房建</t>
+        </is>
+      </c>
+      <c r="AT74" s="3" t="inlineStr">
+        <is>
+          <t>房屋建设</t>
+        </is>
+      </c>
+      <c r="AU74" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM74" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="AN74" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="AO74" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP74" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AQ74" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AR74" s="3" t="inlineStr">
-        <is>
-          <t>产业集团</t>
-        </is>
-      </c>
-      <c r="AS74" s="3" t="inlineStr">
-        <is>
-          <t>产业集团</t>
-        </is>
-      </c>
-      <c r="AT74" s="3" t="inlineStr">
-        <is>
-          <t>石油化工</t>
-        </is>
-      </c>
-      <c r="AU74" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV74" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -17455,12 +17457,14 @@
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="AZ74" s="3"/>
+      <c r="AZ74" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="75" customHeight="true" ht="18.0">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>26京城建SCP007</t>
+          <t>26湖交投MTN003</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -17470,12 +17474,12 @@
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>012682291.IB</t>
+          <t>102683701.IB</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>0.16Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E75" s="4" t="n">
@@ -17486,48 +17490,48 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>1.25 ~ 1.50</t>
+          <t>1.40 ~ 2.40</t>
         </is>
       </c>
       <c r="H75" s="4" t="n">
-        <v>1.31</v>
+        <v>1.65</v>
       </c>
       <c r="I75" s="4" t="n">
-        <v>13.0</v>
+        <v>23.94</v>
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>26京城建SCP005</t>
+          <t>26湖交投MTN002</t>
         </is>
       </c>
       <c r="L75" s="3" t="inlineStr">
         <is>
-          <t>33D</t>
+          <t>2.56Y+2.00Y</t>
         </is>
       </c>
       <c r="M75" s="3" t="inlineStr">
         <is>
-          <t>1.4998</t>
+          <t>1.6792</t>
         </is>
       </c>
       <c r="N75" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7000/--</t>
         </is>
       </c>
       <c r="O75" s="3" t="inlineStr">
         <is>
-          <t>北京城建集团有限责任公司</t>
+          <t>湖州市交通投资集团有限公司</t>
         </is>
       </c>
       <c r="P75" s="3" t="inlineStr">
         <is>
-          <t>C- 23.27</t>
+          <t>C 29.04</t>
         </is>
       </c>
       <c r="Q75" s="3" t="inlineStr">
@@ -17537,7 +17541,7 @@
       </c>
       <c r="R75" s="3" t="inlineStr">
         <is>
-          <t>09-17 09:00</t>
+          <t>09-17 14:00</t>
         </is>
       </c>
       <c r="S75" s="3" t="inlineStr">
@@ -17551,19 +17555,17 @@
         </is>
       </c>
       <c r="U75" s="4" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V75" s="4" t="n">
-        <v>1.0</v>
-      </c>
+        <v>6.8</v>
+      </c>
+      <c r="V75" s="3"/>
       <c r="W75" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X75" s="3" t="inlineStr">
         <is>
-          <t>1.46%~1.50%</t>
+          <t>1.64%~1.74%</t>
         </is>
       </c>
       <c r="Y75" s="3" t="inlineStr">
@@ -17574,23 +17576,23 @@
       <c r="Z75" s="3"/>
       <c r="AA75" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>浙江省-湖州市</t>
         </is>
       </c>
       <c r="AB75" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券发行金额为5亿元，拟全部用于偿还发行人有息债务。</t>
+          <t>发行人本期中期票据基础发行规模为0亿元,发行金额上限为5.00亿元,拟全部用于偿还发行人债务融资工具本金[23湖交投MTN003]</t>
         </is>
       </c>
       <c r="AC75" s="3" t="inlineStr">
         <is>
-          <t>渤海银行股份有限公司,中国民生银行股份有限公司</t>
+          <t>东方证券股份有限公司,招商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD75" s="3"/>
       <c r="AE75" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF75" s="3" t="inlineStr">
@@ -17605,7 +17607,7 @@
       </c>
       <c r="AH75" s="3" t="inlineStr">
         <is>
-          <t>北京城建集团有限责任公司2026年度第七期超短期融资券</t>
+          <t>湖州市交通投资集团有限公司2026年度第三期中期票据</t>
         </is>
       </c>
       <c r="AI75" s="3" t="inlineStr">
@@ -17615,7 +17617,7 @@
       </c>
       <c r="AJ75" s="3" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2031-09-18</t>
         </is>
       </c>
       <c r="AK75" s="3"/>
@@ -17636,37 +17638,37 @@
       </c>
       <c r="AO75" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP75" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ75" s="3" t="inlineStr">
         <is>
-          <t>建筑施工</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR75" s="3" t="inlineStr">
         <is>
-          <t>房屋建筑</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AS75" s="3" t="inlineStr">
         <is>
-          <t>其他房建</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AT75" s="3" t="inlineStr">
         <is>
-          <t>房屋建设</t>
+          <t>高速公路</t>
         </is>
       </c>
       <c r="AU75" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-09-18</t>
         </is>
       </c>
       <c r="AV75" s="3" t="inlineStr">
@@ -17676,7 +17678,7 @@
       </c>
       <c r="AW75" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX75" s="3" t="inlineStr">
@@ -17690,13 +17692,13 @@
         </is>
       </c>
       <c r="AZ75" s="4" t="n">
-        <v>0.0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="76" customHeight="true" ht="18.0">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>26湖交投MTN003</t>
+          <t>26夏商SCP025</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -17706,12 +17708,12 @@
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>102683701.IB</t>
+          <t>012690002.IB</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>0.17Y</t>
         </is>
       </c>
       <c r="E76" s="4" t="n">
@@ -17722,48 +17724,48 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
+          <t>1.30 ~ 1.51</t>
         </is>
       </c>
       <c r="H76" s="4" t="n">
-        <v>1.65</v>
+        <v>1.51</v>
       </c>
       <c r="I76" s="4" t="n">
-        <v>23.94</v>
+        <v>33.0</v>
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="K76" s="3" t="inlineStr">
         <is>
-          <t>26湖交投MTN002</t>
+          <t>26夏商SCP023</t>
         </is>
       </c>
       <c r="L76" s="3" t="inlineStr">
         <is>
-          <t>2.56Y+2.00Y</t>
+          <t>50D</t>
         </is>
       </c>
       <c r="M76" s="3" t="inlineStr">
         <is>
-          <t>1.6792</t>
+          <t>1.5100</t>
         </is>
       </c>
       <c r="N76" s="3" t="inlineStr">
         <is>
-          <t>1.7000/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O76" s="3" t="inlineStr">
         <is>
-          <t>湖州市交通投资集团有限公司</t>
+          <t>厦门夏商集团有限公司</t>
         </is>
       </c>
       <c r="P76" s="3" t="inlineStr">
         <is>
-          <t>C 29.04</t>
+          <t>B- 48.89</t>
         </is>
       </c>
       <c r="Q76" s="3" t="inlineStr">
@@ -17773,7 +17775,7 @@
       </c>
       <c r="R76" s="3" t="inlineStr">
         <is>
-          <t>09-17 14:00</t>
+          <t>09-17 09:00</t>
         </is>
       </c>
       <c r="S76" s="3" t="inlineStr">
@@ -17787,7 +17789,7 @@
         </is>
       </c>
       <c r="U76" s="4" t="n">
-        <v>6.8</v>
+        <v>0.26</v>
       </c>
       <c r="V76" s="3"/>
       <c r="W76" s="3" t="inlineStr">
@@ -17797,34 +17799,34 @@
       </c>
       <c r="X76" s="3" t="inlineStr">
         <is>
-          <t>1.64%~1.74%</t>
+          <t>1.48%~1.52%</t>
         </is>
       </c>
       <c r="Y76" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z76" s="3"/>
       <c r="AA76" s="3" t="inlineStr">
         <is>
-          <t>浙江省-湖州市</t>
+          <t>福建省-厦门市</t>
         </is>
       </c>
       <c r="AB76" s="3" t="inlineStr">
         <is>
-          <t>发行人本期中期票据基础发行规模为0亿元,发行金额上限为5.00亿元,拟全部用于偿还发行人债务融资工具本金[23湖交投MTN003]</t>
+          <t>发行人本期发行超短期融资券5亿元，扣除承销费后全部用于偿还发行人本部即将到期的银行借款本金。</t>
         </is>
       </c>
       <c r="AC76" s="3" t="inlineStr">
         <is>
-          <t>东方证券股份有限公司,招商银行股份有限公司</t>
+          <t>厦门银行股份有限公司,中国国际金融股份有限公司</t>
         </is>
       </c>
       <c r="AD76" s="3"/>
       <c r="AE76" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF76" s="3" t="inlineStr">
@@ -17839,7 +17841,7 @@
       </c>
       <c r="AH76" s="3" t="inlineStr">
         <is>
-          <t>湖州市交通投资集团有限公司2026年度第三期中期票据</t>
+          <t>厦门夏商集团有限公司2026年度第二十五期超短期融资券</t>
         </is>
       </c>
       <c r="AI76" s="3" t="inlineStr">
@@ -17849,7 +17851,7 @@
       </c>
       <c r="AJ76" s="3" t="inlineStr">
         <is>
-          <t>2031-09-18</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="AK76" s="3"/>
@@ -17870,37 +17872,37 @@
       </c>
       <c r="AO76" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP76" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ76" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>贸易零售</t>
         </is>
       </c>
       <c r="AR76" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>其他贸易</t>
         </is>
       </c>
       <c r="AS76" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>其他贸易</t>
         </is>
       </c>
       <c r="AT76" s="3" t="inlineStr">
         <is>
-          <t>高速公路</t>
+          <t>贸易</t>
         </is>
       </c>
       <c r="AU76" s="3" t="inlineStr">
         <is>
-          <t>2029-09-18</t>
+          <t/>
         </is>
       </c>
       <c r="AV76" s="3" t="inlineStr">
@@ -17910,7 +17912,7 @@
       </c>
       <c r="AW76" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX76" s="3" t="inlineStr">
@@ -17923,14 +17925,12 @@
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="AZ76" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ76" s="3"/>
     </row>
     <row r="77" customHeight="true" ht="18.0">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>26夏商SCP025</t>
+          <t>26凯盛科技MTN002</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -17940,64 +17940,64 @@
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>012690002.IB</t>
+          <t>102683714.IB</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>0.17Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E77" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.51</t>
+          <t>1.50 ~ 1.74</t>
         </is>
       </c>
       <c r="H77" s="4" t="n">
-        <v>1.51</v>
+        <v>1.74</v>
       </c>
       <c r="I77" s="4" t="n">
-        <v>33.0</v>
+        <v>48.21</v>
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t>26夏商SCP023</t>
+          <t>25凯盛K1</t>
         </is>
       </c>
       <c r="L77" s="3" t="inlineStr">
         <is>
-          <t>50D</t>
+          <t>1.95Y</t>
         </is>
       </c>
       <c r="M77" s="3" t="inlineStr">
         <is>
-          <t>1.5100</t>
+          <t>1.6781</t>
         </is>
       </c>
       <c r="N77" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.6400</t>
         </is>
       </c>
       <c r="O77" s="3" t="inlineStr">
         <is>
-          <t>厦门夏商集团有限公司</t>
+          <t>凯盛科技集团有限公司</t>
         </is>
       </c>
       <c r="P77" s="3" t="inlineStr">
         <is>
-          <t>B- 48.89</t>
+          <t>B- 41.35</t>
         </is>
       </c>
       <c r="Q77" s="3" t="inlineStr">
@@ -18021,49 +18021,49 @@
         </is>
       </c>
       <c r="U77" s="4" t="n">
-        <v>0.26</v>
+        <v>0.89</v>
       </c>
       <c r="V77" s="3"/>
       <c r="W77" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X77" s="3" t="inlineStr">
         <is>
-          <t>1.48%~1.52%</t>
+          <t>1.68%~1.78%</t>
         </is>
       </c>
       <c r="Y77" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z77" s="3"/>
       <c r="AA77" s="3" t="inlineStr">
         <is>
-          <t>福建省-厦门市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB77" s="3" t="inlineStr">
         <is>
-          <t>发行人本期发行超短期融资券5亿元，扣除承销费后全部用于偿还发行人本部即将到期的银行借款本金。</t>
+          <t>本期中期票据募集资金10亿元,拟用于偿还带息债务以及补充公司日常生产经营所需流动资金。</t>
         </is>
       </c>
       <c r="AC77" s="3" t="inlineStr">
         <is>
-          <t>厦门银行股份有限公司,中国国际金融股份有限公司</t>
+          <t>北京银行股份有限公司,中国邮政储蓄银行股份有限公司</t>
         </is>
       </c>
       <c r="AD77" s="3"/>
       <c r="AE77" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF77" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG77" s="3" t="inlineStr">
@@ -18073,7 +18073,7 @@
       </c>
       <c r="AH77" s="3" t="inlineStr">
         <is>
-          <t>厦门夏商集团有限公司2026年度第二十五期超短期融资券</t>
+          <t>凯盛科技集团有限公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI77" s="3" t="inlineStr">
@@ -18083,7 +18083,7 @@
       </c>
       <c r="AJ77" s="3" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2029-09-18</t>
         </is>
       </c>
       <c r="AK77" s="3"/>
@@ -18109,27 +18109,27 @@
       </c>
       <c r="AP77" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ77" s="3" t="inlineStr">
         <is>
-          <t>贸易零售</t>
+          <t>化工制造</t>
         </is>
       </c>
       <c r="AR77" s="3" t="inlineStr">
         <is>
-          <t>其他贸易</t>
+          <t>新材料</t>
         </is>
       </c>
       <c r="AS77" s="3" t="inlineStr">
         <is>
-          <t>其他贸易</t>
+          <t>新材料</t>
         </is>
       </c>
       <c r="AT77" s="3" t="inlineStr">
         <is>
-          <t>贸易</t>
+          <t>玻璃制造</t>
         </is>
       </c>
       <c r="AU77" s="3" t="inlineStr">
@@ -18162,7 +18162,7 @@
     <row r="78" customHeight="true" ht="18.0">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>26凯盛科技MTN002</t>
+          <t>26济南城建MTN002</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -18172,12 +18172,12 @@
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>102683714.IB</t>
+          <t>102683708.IB</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E78" s="4" t="n">
@@ -18188,48 +18188,48 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 1.74</t>
+          <t>1.50 ~ 2.10</t>
         </is>
       </c>
       <c r="H78" s="4" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="I78" s="4" t="n">
-        <v>48.21</v>
+        <v>34.94</v>
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="K78" s="3" t="inlineStr">
         <is>
-          <t>25凯盛K1</t>
+          <t>26济南城建MTN001</t>
         </is>
       </c>
       <c r="L78" s="3" t="inlineStr">
         <is>
-          <t>1.95Y</t>
+          <t>4.96Y</t>
         </is>
       </c>
       <c r="M78" s="3" t="inlineStr">
         <is>
-          <t>1.6781</t>
+          <t>1.7835</t>
         </is>
       </c>
       <c r="N78" s="3" t="inlineStr">
         <is>
-          <t>--/1.6400</t>
+          <t>1.8200/1.7700</t>
         </is>
       </c>
       <c r="O78" s="3" t="inlineStr">
         <is>
-          <t>凯盛科技集团有限公司</t>
+          <t>济南城市建设集团有限公司</t>
         </is>
       </c>
       <c r="P78" s="3" t="inlineStr">
         <is>
-          <t>B- 41.35</t>
+          <t>C+ 31.87</t>
         </is>
       </c>
       <c r="Q78" s="3" t="inlineStr">
@@ -18253,17 +18253,19 @@
         </is>
       </c>
       <c r="U78" s="4" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="V78" s="3"/>
+        <v>6.15</v>
+      </c>
+      <c r="V78" s="4" t="n">
+        <v>3.7</v>
+      </c>
       <c r="W78" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X78" s="3" t="inlineStr">
         <is>
-          <t>1.68%~1.78%</t>
+          <t>1.74%~1.84%</t>
         </is>
       </c>
       <c r="Y78" s="3" t="inlineStr">
@@ -18274,17 +18276,17 @@
       <c r="Z78" s="3"/>
       <c r="AA78" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>山东省-济南市</t>
         </is>
       </c>
       <c r="AB78" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据募集资金10亿元,拟用于偿还带息债务以及补充公司日常生产经营所需流动资金。</t>
+          <t>本期中期票据发行金额为10亿元,用于偿还发行人已到期的债务融资工具本金。[25济南城建SCP007]</t>
         </is>
       </c>
       <c r="AC78" s="3" t="inlineStr">
         <is>
-          <t>北京银行股份有限公司,中国邮政储蓄银行股份有限公司</t>
+          <t>北京银行股份有限公司,上海浦东发展银行股份有限公司</t>
         </is>
       </c>
       <c r="AD78" s="3"/>
@@ -18295,7 +18297,7 @@
       </c>
       <c r="AF78" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG78" s="3" t="inlineStr">
@@ -18305,7 +18307,7 @@
       </c>
       <c r="AH78" s="3" t="inlineStr">
         <is>
-          <t>凯盛科技集团有限公司2026年度第二期中期票据</t>
+          <t>济南城市建设集团有限公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI78" s="3" t="inlineStr">
@@ -18315,7 +18317,7 @@
       </c>
       <c r="AJ78" s="3" t="inlineStr">
         <is>
-          <t>2029-09-18</t>
+          <t>2031-09-18</t>
         </is>
       </c>
       <c r="AK78" s="3"/>
@@ -18341,27 +18343,27 @@
       </c>
       <c r="AP78" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ78" s="3" t="inlineStr">
         <is>
-          <t>化工制造</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR78" s="3" t="inlineStr">
         <is>
-          <t>新材料</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS78" s="3" t="inlineStr">
         <is>
-          <t>新材料</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT78" s="3" t="inlineStr">
         <is>
-          <t>玻璃制造</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU78" s="3" t="inlineStr">
@@ -18389,12 +18391,14 @@
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="AZ78" s="3"/>
+      <c r="AZ78" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="79" customHeight="true" ht="18.0">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>26济南城建MTN002</t>
+          <t>26深燃气SCP004</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -18404,12 +18408,12 @@
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>102683708.IB</t>
+          <t>012682300.IB</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E79" s="4" t="n">
@@ -18420,48 +18424,48 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.10</t>
+          <t>1.30 ~ 1.70</t>
         </is>
       </c>
       <c r="H79" s="4" t="n">
-        <v>1.76</v>
+        <v>1.38</v>
       </c>
       <c r="I79" s="4" t="n">
-        <v>34.94</v>
+        <v>17.33</v>
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>26济南城建MTN001</t>
+          <t>26深燃气SCP002</t>
         </is>
       </c>
       <c r="L79" s="3" t="inlineStr">
         <is>
-          <t>4.96Y</t>
+          <t>204D</t>
         </is>
       </c>
       <c r="M79" s="3" t="inlineStr">
         <is>
-          <t>1.7835</t>
+          <t>1.5127</t>
         </is>
       </c>
       <c r="N79" s="3" t="inlineStr">
         <is>
-          <t>1.8200/1.7700</t>
+          <t>1.5000/--</t>
         </is>
       </c>
       <c r="O79" s="3" t="inlineStr">
         <is>
-          <t>济南城市建设集团有限公司</t>
+          <t>深圳市燃气集团股份有限公司</t>
         </is>
       </c>
       <c r="P79" s="3" t="inlineStr">
         <is>
-          <t>C+ 31.87</t>
+          <t>B 50.65</t>
         </is>
       </c>
       <c r="Q79" s="3" t="inlineStr">
@@ -18485,19 +18489,19 @@
         </is>
       </c>
       <c r="U79" s="4" t="n">
-        <v>6.15</v>
+        <v>3.19</v>
       </c>
       <c r="V79" s="4" t="n">
-        <v>3.7</v>
+        <v>1.0</v>
       </c>
       <c r="W79" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X79" s="3" t="inlineStr">
         <is>
-          <t>1.74%~1.84%</t>
+          <t>1.50%~1.54%</t>
         </is>
       </c>
       <c r="Y79" s="3" t="inlineStr">
@@ -18508,23 +18512,23 @@
       <c r="Z79" s="3"/>
       <c r="AA79" s="3" t="inlineStr">
         <is>
-          <t>山东省-济南市</t>
+          <t>广东省-深圳市</t>
         </is>
       </c>
       <c r="AB79" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行金额为10亿元,用于偿还发行人已到期的债务融资工具本金。[25济南城建SCP007]</t>
+          <t>本期超短期融资券发行规模为人民币10亿元。发行人拟将本期发行所募集资金的5亿元用于偿还债务融资工具本金、5亿元用于补充流动资金。[25深燃气SCP004(科创债)]</t>
         </is>
       </c>
       <c r="AC79" s="3" t="inlineStr">
         <is>
-          <t>北京银行股份有限公司,上海浦东发展银行股份有限公司</t>
+          <t>江苏银行股份有限公司,兴业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD79" s="3"/>
       <c r="AE79" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF79" s="3" t="inlineStr">
@@ -18539,7 +18543,7 @@
       </c>
       <c r="AH79" s="3" t="inlineStr">
         <is>
-          <t>济南城市建设集团有限公司2026年度第二期中期票据</t>
+          <t>深圳市燃气集团股份有限公司2026年度第四期超短期融资券</t>
         </is>
       </c>
       <c r="AI79" s="3" t="inlineStr">
@@ -18549,7 +18553,7 @@
       </c>
       <c r="AJ79" s="3" t="inlineStr">
         <is>
-          <t>2031-09-18</t>
+          <t>2027-06-15</t>
         </is>
       </c>
       <c r="AK79" s="3"/>
@@ -18575,27 +18579,27 @@
       </c>
       <c r="AP79" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ79" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR79" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>燃气</t>
         </is>
       </c>
       <c r="AS79" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>燃气</t>
         </is>
       </c>
       <c r="AT79" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>燃气</t>
         </is>
       </c>
       <c r="AU79" s="3" t="inlineStr">
@@ -18624,13 +18628,13 @@
         </is>
       </c>
       <c r="AZ79" s="4" t="n">
-        <v>0.01</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="80" customHeight="true" ht="18.0">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>26深燃气SCP004</t>
+          <t>26晋能电力MTN007</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -18640,12 +18644,12 @@
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>012682300.IB</t>
+          <t>102683693.IB</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>7Y</t>
         </is>
       </c>
       <c r="E80" s="4" t="n">
@@ -18656,48 +18660,48 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.70</t>
+          <t>1.50 ~ 2.12</t>
         </is>
       </c>
       <c r="H80" s="4" t="n">
-        <v>1.38</v>
+        <v>2.11</v>
       </c>
       <c r="I80" s="4" t="n">
-        <v>17.33</v>
+        <v>59.57</v>
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="K80" s="3" t="inlineStr">
         <is>
-          <t>26深燃气SCP002</t>
+          <t>26晋能电力MTN002</t>
         </is>
       </c>
       <c r="L80" s="3" t="inlineStr">
         <is>
-          <t>204D</t>
+          <t>6.52Y</t>
         </is>
       </c>
       <c r="M80" s="3" t="inlineStr">
         <is>
-          <t>1.5127</t>
+          <t>2.1010</t>
         </is>
       </c>
       <c r="N80" s="3" t="inlineStr">
         <is>
-          <t>1.5000/--</t>
+          <t>--/2.0700</t>
         </is>
       </c>
       <c r="O80" s="3" t="inlineStr">
         <is>
-          <t>深圳市燃气集团股份有限公司</t>
+          <t>晋能控股电力集团有限公司</t>
         </is>
       </c>
       <c r="P80" s="3" t="inlineStr">
         <is>
-          <t>B 50.65</t>
+          <t>C+ 32.21</t>
         </is>
       </c>
       <c r="Q80" s="3" t="inlineStr">
@@ -18707,7 +18711,7 @@
       </c>
       <c r="R80" s="3" t="inlineStr">
         <is>
-          <t>09-17 09:00</t>
+          <t>09-17 11:00</t>
         </is>
       </c>
       <c r="S80" s="3" t="inlineStr">
@@ -18721,19 +18725,19 @@
         </is>
       </c>
       <c r="U80" s="4" t="n">
-        <v>3.19</v>
+        <v>1.34</v>
       </c>
       <c r="V80" s="4" t="n">
-        <v>1.0</v>
+        <v>2.8</v>
       </c>
       <c r="W80" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X80" s="3" t="inlineStr">
         <is>
-          <t>1.50%~1.54%</t>
+          <t>2.18%~2.28%</t>
         </is>
       </c>
       <c r="Y80" s="3" t="inlineStr">
@@ -18744,23 +18748,23 @@
       <c r="Z80" s="3"/>
       <c r="AA80" s="3" t="inlineStr">
         <is>
-          <t>广东省-深圳市</t>
+          <t>山西省-太原市</t>
         </is>
       </c>
       <c r="AB80" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券发行规模为人民币10亿元。发行人拟将本期发行所募集资金的5亿元用于偿还债务融资工具本金、5亿元用于补充流动资金。[25深燃气SCP004(科创债)]</t>
+          <t>发行人本期中期票据发行采用发行金额动态调整机制，基础发行规模人民币0.00亿元，发行上限金额人民币10.00亿元，发行人将根据本次发行结果将募集资金用于偿还公司本部及子公司有息债务及相关财务费用。</t>
         </is>
       </c>
       <c r="AC80" s="3" t="inlineStr">
         <is>
-          <t>江苏银行股份有限公司,兴业银行股份有限公司</t>
+          <t>兴业银行股份有限公司,兴业证券股份有限公司</t>
         </is>
       </c>
       <c r="AD80" s="3"/>
       <c r="AE80" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF80" s="3" t="inlineStr">
@@ -18775,7 +18779,7 @@
       </c>
       <c r="AH80" s="3" t="inlineStr">
         <is>
-          <t>深圳市燃气集团股份有限公司2026年度第四期超短期融资券</t>
+          <t>晋能控股电力集团有限公司2026年度第七期中期票据</t>
         </is>
       </c>
       <c r="AI80" s="3" t="inlineStr">
@@ -18785,10 +18789,14 @@
       </c>
       <c r="AJ80" s="3" t="inlineStr">
         <is>
-          <t>2027-06-15</t>
-        </is>
-      </c>
-      <c r="AK80" s="3"/>
+          <t>2033-09-18</t>
+        </is>
+      </c>
+      <c r="AK80" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL80" s="3" t="inlineStr">
         <is>
           <t>2026-09-20</t>
@@ -18811,27 +18819,27 @@
       </c>
       <c r="AP80" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ80" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>化石能源</t>
         </is>
       </c>
       <c r="AR80" s="3" t="inlineStr">
         <is>
-          <t>燃气</t>
+          <t>煤炭</t>
         </is>
       </c>
       <c r="AS80" s="3" t="inlineStr">
         <is>
-          <t>燃气</t>
+          <t>其他煤炭</t>
         </is>
       </c>
       <c r="AT80" s="3" t="inlineStr">
         <is>
-          <t>燃气</t>
+          <t>煤炭开采</t>
         </is>
       </c>
       <c r="AU80" s="3" t="inlineStr">
@@ -18866,7 +18874,7 @@
     <row r="81" customHeight="true" ht="18.0">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>26晋能电力MTN007</t>
+          <t>26国能江苏SCP008</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -18876,64 +18884,64 @@
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>102683693.IB</t>
+          <t>012682299.IB</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>7Y</t>
+          <t>0.26Y</t>
         </is>
       </c>
       <c r="E81" s="4" t="n">
-        <v>10.0</v>
+        <v>3.0</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>10.0</v>
+        <v>3.0</v>
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.12</t>
+          <t>1.30 ~ 1.70</t>
         </is>
       </c>
       <c r="H81" s="4" t="n">
-        <v>2.11</v>
+        <v>1.39</v>
       </c>
       <c r="I81" s="4" t="n">
-        <v>59.57</v>
+        <v>20.77</v>
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="K81" s="3" t="inlineStr">
         <is>
-          <t>26晋能电力MTN002</t>
+          <t>26国能江苏SCP002</t>
         </is>
       </c>
       <c r="L81" s="3" t="inlineStr">
         <is>
-          <t>6.52Y</t>
+          <t>120D</t>
         </is>
       </c>
       <c r="M81" s="3" t="inlineStr">
         <is>
-          <t>2.1010</t>
+          <t>1.4932</t>
         </is>
       </c>
       <c r="N81" s="3" t="inlineStr">
         <is>
-          <t>--/2.0700</t>
+          <t>1.5200/--</t>
         </is>
       </c>
       <c r="O81" s="3" t="inlineStr">
         <is>
-          <t>晋能控股电力集团有限公司</t>
+          <t>国家能源集团江苏电力有限公司</t>
         </is>
       </c>
       <c r="P81" s="3" t="inlineStr">
         <is>
-          <t>C+ 32.21</t>
+          <t>D+ 9.42</t>
         </is>
       </c>
       <c r="Q81" s="3" t="inlineStr">
@@ -18943,7 +18951,7 @@
       </c>
       <c r="R81" s="3" t="inlineStr">
         <is>
-          <t>09-17 11:00</t>
+          <t>09-17 09:00</t>
         </is>
       </c>
       <c r="S81" s="3" t="inlineStr">
@@ -18957,19 +18965,17 @@
         </is>
       </c>
       <c r="U81" s="4" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="V81" s="4" t="n">
         <v>2.8</v>
       </c>
+      <c r="V81" s="3"/>
       <c r="W81" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X81" s="3" t="inlineStr">
         <is>
-          <t>2.18%~2.28%</t>
+          <t>1.47%~1.51%</t>
         </is>
       </c>
       <c r="Y81" s="3" t="inlineStr">
@@ -18980,28 +18986,28 @@
       <c r="Z81" s="3"/>
       <c r="AA81" s="3" t="inlineStr">
         <is>
-          <t>山西省-太原市</t>
+          <t>江苏省-南京市</t>
         </is>
       </c>
       <c r="AB81" s="3" t="inlineStr">
         <is>
-          <t>发行人本期中期票据发行采用发行金额动态调整机制，基础发行规模人民币0.00亿元，发行上限金额人民币10.00亿元，发行人将根据本次发行结果将募集资金用于偿还公司本部及子公司有息债务及相关财务费用。</t>
+          <t>本期超短期融资券发行金额3.00亿元,全部用于归还存量到期债务以及补充营运资金。</t>
         </is>
       </c>
       <c r="AC81" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,兴业证券股份有限公司</t>
+          <t>招商银行股份有限公司,南京银行股份有限公司</t>
         </is>
       </c>
       <c r="AD81" s="3"/>
       <c r="AE81" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF81" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG81" s="3" t="inlineStr">
@@ -19011,7 +19017,7 @@
       </c>
       <c r="AH81" s="3" t="inlineStr">
         <is>
-          <t>晋能控股电力集团有限公司2026年度第七期中期票据</t>
+          <t>国家能源集团江苏电力有限公司2026年度第八期超短期融资券</t>
         </is>
       </c>
       <c r="AI81" s="3" t="inlineStr">
@@ -19021,14 +19027,10 @@
       </c>
       <c r="AJ81" s="3" t="inlineStr">
         <is>
-          <t>2033-09-18</t>
-        </is>
-      </c>
-      <c r="AK81" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2026-12-23</t>
+        </is>
+      </c>
+      <c r="AK81" s="3"/>
       <c r="AL81" s="3" t="inlineStr">
         <is>
           <t>2026-09-20</t>
@@ -19051,27 +19053,27 @@
       </c>
       <c r="AP81" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ81" s="3" t="inlineStr">
         <is>
-          <t>化石能源</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR81" s="3" t="inlineStr">
         <is>
-          <t>煤炭</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AS81" s="3" t="inlineStr">
         <is>
-          <t>其他煤炭</t>
+          <t>火电</t>
         </is>
       </c>
       <c r="AT81" s="3" t="inlineStr">
         <is>
-          <t>煤炭开采</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AU81" s="3" t="inlineStr">
@@ -19099,14 +19101,12 @@
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="AZ81" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ81" s="3"/>
     </row>
     <row r="82" customHeight="true" ht="18.0">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>26国能江苏SCP008</t>
+          <t>26立讯精工SCP007</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -19116,64 +19116,64 @@
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>012682299.IB</t>
+          <t>012682288.IB</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>0.26Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E82" s="4" t="n">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.70</t>
+          <t>1.25 ~ 1.55</t>
         </is>
       </c>
       <c r="H82" s="4" t="n">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="I82" s="4" t="n">
-        <v>20.77</v>
+        <v>25.33</v>
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="K82" s="3" t="inlineStr">
         <is>
-          <t>26国能江苏SCP002</t>
+          <t>26立讯精工SCP005</t>
         </is>
       </c>
       <c r="L82" s="3" t="inlineStr">
         <is>
-          <t>120D</t>
+          <t>243D</t>
         </is>
       </c>
       <c r="M82" s="3" t="inlineStr">
         <is>
-          <t>1.4932</t>
+          <t>1.5491</t>
         </is>
       </c>
       <c r="N82" s="3" t="inlineStr">
         <is>
-          <t>1.5200/--</t>
+          <t>1.5700/1.5450</t>
         </is>
       </c>
       <c r="O82" s="3" t="inlineStr">
         <is>
-          <t>国家能源集团江苏电力有限公司</t>
+          <t>立讯精密工业股份有限公司</t>
         </is>
       </c>
       <c r="P82" s="3" t="inlineStr">
         <is>
-          <t>D+ 9.42</t>
+          <t>C- 24.22</t>
         </is>
       </c>
       <c r="Q82" s="3" t="inlineStr">
@@ -19197,38 +19197,40 @@
         </is>
       </c>
       <c r="U82" s="4" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="V82" s="3"/>
+        <v>1.5</v>
+      </c>
+      <c r="V82" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="W82" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X82" s="3" t="inlineStr">
         <is>
-          <t>1.47%~1.51%</t>
+          <t>1.55%~1.59%</t>
         </is>
       </c>
       <c r="Y82" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南京市</t>
+          <t>广东省-深圳市</t>
         </is>
       </c>
       <c r="AB82" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券发行金额3.00亿元,全部用于归还存量到期债务以及补充营运资金。</t>
+          <t>本期超短期融资券发行金额为10亿元，拟用于偿还发行人存量有息债务。</t>
         </is>
       </c>
       <c r="AC82" s="3" t="inlineStr">
         <is>
-          <t>招商银行股份有限公司,南京银行股份有限公司</t>
+          <t>上海银行股份有限公司,广发银行股份有限公司,兴业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD82" s="3"/>
@@ -19239,7 +19241,7 @@
       </c>
       <c r="AF82" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>民营企业</t>
         </is>
       </c>
       <c r="AG82" s="3" t="inlineStr">
@@ -19249,7 +19251,7 @@
       </c>
       <c r="AH82" s="3" t="inlineStr">
         <is>
-          <t>国家能源集团江苏电力有限公司2026年度第八期超短期融资券</t>
+          <t>立讯精密工业股份有限公司2026年度第七期超短期融资券</t>
         </is>
       </c>
       <c r="AI82" s="3" t="inlineStr">
@@ -19259,7 +19261,7 @@
       </c>
       <c r="AJ82" s="3" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2027-06-15</t>
         </is>
       </c>
       <c r="AK82" s="3"/>
@@ -19285,27 +19287,27 @@
       </c>
       <c r="AP82" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ82" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>电子制造</t>
         </is>
       </c>
       <c r="AR82" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>电子元器件</t>
         </is>
       </c>
       <c r="AS82" s="3" t="inlineStr">
         <is>
-          <t>火电</t>
+          <t>电子元器件</t>
         </is>
       </c>
       <c r="AT82" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>电子制造</t>
         </is>
       </c>
       <c r="AU82" s="3" t="inlineStr">
@@ -19338,7 +19340,7 @@
     <row r="83" customHeight="true" ht="18.0">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>26立讯精工SCP007</t>
+          <t>26上虞国投MTN004</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -19348,64 +19350,64 @@
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>012682288.IB</t>
+          <t>102690042.IB</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E83" s="4" t="n">
-        <v>10.0</v>
+        <v>4.0</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>10.0</v>
+        <v>4.0</v>
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>1.25 ~ 1.55</t>
+          <t>1.40 ~ 2.40</t>
         </is>
       </c>
       <c r="H83" s="4" t="n">
-        <v>1.46</v>
+        <v>1.68</v>
       </c>
       <c r="I83" s="4" t="n">
-        <v>25.33</v>
+        <v>26.94</v>
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="K83" s="3" t="inlineStr">
         <is>
-          <t>26立讯精工SCP005</t>
+          <t>24上虞国投MTN002</t>
         </is>
       </c>
       <c r="L83" s="3" t="inlineStr">
         <is>
-          <t>243D</t>
+          <t>2.91Y</t>
         </is>
       </c>
       <c r="M83" s="3" t="inlineStr">
         <is>
-          <t>1.5491</t>
+          <t>1.7008</t>
         </is>
       </c>
       <c r="N83" s="3" t="inlineStr">
         <is>
-          <t>1.5700/1.5450</t>
+          <t>1.7300/--</t>
         </is>
       </c>
       <c r="O83" s="3" t="inlineStr">
         <is>
-          <t>立讯精密工业股份有限公司</t>
+          <t>绍兴市上虞区国有资本投资运营有限公司</t>
         </is>
       </c>
       <c r="P83" s="3" t="inlineStr">
         <is>
-          <t>C- 24.22</t>
+          <t>C 29.68</t>
         </is>
       </c>
       <c r="Q83" s="3" t="inlineStr">
@@ -19415,7 +19417,7 @@
       </c>
       <c r="R83" s="3" t="inlineStr">
         <is>
-          <t>09-17 09:00</t>
+          <t>09-17 14:00</t>
         </is>
       </c>
       <c r="S83" s="3" t="inlineStr">
@@ -19429,19 +19431,17 @@
         </is>
       </c>
       <c r="U83" s="4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V83" s="4" t="n">
-        <v>1.0</v>
-      </c>
+        <v>7.275</v>
+      </c>
+      <c r="V83" s="3"/>
       <c r="W83" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X83" s="3" t="inlineStr">
         <is>
-          <t>1.55%~1.59%</t>
+          <t>1.65%~1.75%</t>
         </is>
       </c>
       <c r="Y83" s="3" t="inlineStr">
@@ -19452,28 +19452,28 @@
       <c r="Z83" s="3"/>
       <c r="AA83" s="3" t="inlineStr">
         <is>
-          <t>广东省-深圳市</t>
+          <t>浙江省-绍兴市</t>
         </is>
       </c>
       <c r="AB83" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券发行金额为10亿元，拟用于偿还发行人存量有息债务。</t>
+          <t>本期基础发行规模0亿元,发行金额上限为4.00亿元,拟全部用于偿还发行人即将到期的债务融资工具本金[23上虞国投PPN002]</t>
         </is>
       </c>
       <c r="AC83" s="3" t="inlineStr">
         <is>
-          <t>上海银行股份有限公司,广发银行股份有限公司,兴业银行股份有限公司</t>
+          <t>中信证券股份有限公司,杭州银行股份有限公司</t>
         </is>
       </c>
       <c r="AD83" s="3"/>
       <c r="AE83" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF83" s="3" t="inlineStr">
         <is>
-          <t>民营企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG83" s="3" t="inlineStr">
@@ -19483,7 +19483,7 @@
       </c>
       <c r="AH83" s="3" t="inlineStr">
         <is>
-          <t>立讯精密工业股份有限公司2026年度第七期超短期融资券</t>
+          <t>绍兴市上虞区国有资本投资运营有限公司2026年度第四期中期票据</t>
         </is>
       </c>
       <c r="AI83" s="3" t="inlineStr">
@@ -19493,7 +19493,7 @@
       </c>
       <c r="AJ83" s="3" t="inlineStr">
         <is>
-          <t>2027-06-15</t>
+          <t>2031-09-18</t>
         </is>
       </c>
       <c r="AK83" s="3"/>
@@ -19514,37 +19514,37 @@
       </c>
       <c r="AO83" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP83" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ83" s="3" t="inlineStr">
         <is>
-          <t>电子制造</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR83" s="3" t="inlineStr">
         <is>
-          <t>电子元器件</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS83" s="3" t="inlineStr">
         <is>
-          <t>电子元器件</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT83" s="3" t="inlineStr">
         <is>
-          <t>电子制造</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU83" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-09-18</t>
         </is>
       </c>
       <c r="AV83" s="3" t="inlineStr">
@@ -19554,7 +19554,7 @@
       </c>
       <c r="AW83" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX83" s="3" t="inlineStr">
@@ -19567,12 +19567,14 @@
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="AZ83" s="3"/>
+      <c r="AZ83" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="84" customHeight="true" ht="18.0">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>26上虞国投MTN004</t>
+          <t>26安瑞科控SCP002</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -19582,64 +19584,64 @@
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>102690042.IB</t>
+          <t>012682287.IB</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E84" s="4" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
+          <t>1.40 ~ 1.80</t>
         </is>
       </c>
       <c r="H84" s="4" t="n">
-        <v>1.68</v>
+        <v>1.49</v>
       </c>
       <c r="I84" s="4" t="n">
-        <v>26.94</v>
+        <v>28.33</v>
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="K84" s="3" t="inlineStr">
         <is>
-          <t>24上虞国投MTN002</t>
+          <t>24安瑞科控MTN001</t>
         </is>
       </c>
       <c r="L84" s="3" t="inlineStr">
         <is>
-          <t>2.91Y</t>
+          <t>219D</t>
         </is>
       </c>
       <c r="M84" s="3" t="inlineStr">
         <is>
-          <t>1.7008</t>
+          <t>1.5967</t>
         </is>
       </c>
       <c r="N84" s="3" t="inlineStr">
         <is>
-          <t>1.7300/--</t>
+          <t>1.6000/1.5600</t>
         </is>
       </c>
       <c r="O84" s="3" t="inlineStr">
         <is>
-          <t>绍兴市上虞区国有资本投资运营有限公司</t>
+          <t>中集安瑞科控股有限公司</t>
         </is>
       </c>
       <c r="P84" s="3" t="inlineStr">
         <is>
-          <t>C 29.68</t>
+          <t>C- 22.86</t>
         </is>
       </c>
       <c r="Q84" s="3" t="inlineStr">
@@ -19649,7 +19651,7 @@
       </c>
       <c r="R84" s="3" t="inlineStr">
         <is>
-          <t>09-17 14:00</t>
+          <t>09-17 09:00</t>
         </is>
       </c>
       <c r="S84" s="3" t="inlineStr">
@@ -19663,7 +19665,7 @@
         </is>
       </c>
       <c r="U84" s="4" t="n">
-        <v>7.275</v>
+        <v>4.6</v>
       </c>
       <c r="V84" s="3"/>
       <c r="W84" s="3" t="inlineStr">
@@ -19673,39 +19675,35 @@
       </c>
       <c r="X84" s="3" t="inlineStr">
         <is>
-          <t>1.65%~1.75%</t>
+          <t>1.59%~1.63%</t>
         </is>
       </c>
       <c r="Y84" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z84" s="3"/>
-      <c r="AA84" s="3" t="inlineStr">
-        <is>
-          <t>浙江省-绍兴市</t>
-        </is>
-      </c>
+      <c r="AA84" s="3"/>
       <c r="AB84" s="3" t="inlineStr">
         <is>
-          <t>本期基础发行规模0亿元,发行金额上限为4.00亿元,拟全部用于偿还发行人即将到期的债务融资工具本金[23上虞国投PPN002]</t>
+          <t>本期超短期融资券发行5亿元,全部用于归还发行人到期债券[26安瑞科控SCP001]</t>
         </is>
       </c>
       <c r="AC84" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,杭州银行股份有限公司</t>
+          <t>招商银行股份有限公司,中国工商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD84" s="3"/>
       <c r="AE84" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF84" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>外商独资企业</t>
         </is>
       </c>
       <c r="AG84" s="3" t="inlineStr">
@@ -19715,7 +19713,7 @@
       </c>
       <c r="AH84" s="3" t="inlineStr">
         <is>
-          <t>绍兴市上虞区国有资本投资运营有限公司2026年度第四期中期票据</t>
+          <t>中集安瑞科控股有限公司2026年度第二期超短期融资券</t>
         </is>
       </c>
       <c r="AI84" s="3" t="inlineStr">
@@ -19725,7 +19723,7 @@
       </c>
       <c r="AJ84" s="3" t="inlineStr">
         <is>
-          <t>2031-09-18</t>
+          <t>2027-06-15</t>
         </is>
       </c>
       <c r="AK84" s="3"/>
@@ -19746,37 +19744,33 @@
       </c>
       <c r="AO84" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP84" s="3" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP84" s="3"/>
       <c r="AQ84" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>其他设备制造</t>
         </is>
       </c>
       <c r="AR84" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>其他专用设备</t>
         </is>
       </c>
       <c r="AS84" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>其他专用设备</t>
         </is>
       </c>
       <c r="AT84" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>石油化工</t>
         </is>
       </c>
       <c r="AU84" s="3" t="inlineStr">
         <is>
-          <t>2029-09-18</t>
+          <t/>
         </is>
       </c>
       <c r="AV84" s="3" t="inlineStr">
@@ -19786,7 +19780,7 @@
       </c>
       <c r="AW84" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX84" s="3" t="inlineStr">
@@ -19806,7 +19800,7 @@
     <row r="85" customHeight="true" ht="18.0">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>26安瑞科控SCP002</t>
+          <t>26招商局SCP006</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
@@ -19816,7 +19810,7 @@
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>012682287.IB</t>
+          <t>012682292.IB</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
@@ -19825,55 +19819,55 @@
         </is>
       </c>
       <c r="E85" s="4" t="n">
-        <v>5.0</v>
+        <v>50.0</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>5.0</v>
+        <v>50.0</v>
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 1.80</t>
+          <t>1.25 ~ 1.65</t>
         </is>
       </c>
       <c r="H85" s="4" t="n">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="I85" s="4" t="n">
-        <v>28.33</v>
+        <v>21.33</v>
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="K85" s="3" t="inlineStr">
         <is>
-          <t>24安瑞科控MTN001</t>
+          <t>26招商局SCP005</t>
         </is>
       </c>
       <c r="L85" s="3" t="inlineStr">
         <is>
-          <t>219D</t>
+          <t>126D</t>
         </is>
       </c>
       <c r="M85" s="3" t="inlineStr">
         <is>
-          <t>1.5967</t>
+          <t>1.4800</t>
         </is>
       </c>
       <c r="N85" s="3" t="inlineStr">
         <is>
-          <t>1.6000/1.5600</t>
+          <t>--/1.4700</t>
         </is>
       </c>
       <c r="O85" s="3" t="inlineStr">
         <is>
-          <t>中集安瑞科控股有限公司</t>
+          <t>招商局集团有限公司</t>
         </is>
       </c>
       <c r="P85" s="3" t="inlineStr">
         <is>
-          <t>C- 22.86</t>
+          <t>B 54.02</t>
         </is>
       </c>
       <c r="Q85" s="3" t="inlineStr">
@@ -19897,17 +19891,17 @@
         </is>
       </c>
       <c r="U85" s="4" t="n">
-        <v>4.6</v>
+        <v>1.94</v>
       </c>
       <c r="V85" s="3"/>
       <c r="W85" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="X85" s="3" t="inlineStr">
         <is>
-          <t>1.59%~1.63%</t>
+          <t>1.48%~1.52%</t>
         </is>
       </c>
       <c r="Y85" s="3" t="inlineStr">
@@ -19916,15 +19910,19 @@
         </is>
       </c>
       <c r="Z85" s="3"/>
-      <c r="AA85" s="3"/>
+      <c r="AA85" s="3" t="inlineStr">
+        <is>
+          <t>北京市</t>
+        </is>
+      </c>
       <c r="AB85" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券发行5亿元,全部用于归还发行人到期债券[26安瑞科控SCP001]</t>
+          <t>公司此次发行50亿元超短期融资券,募集资金拟用于偿还发行人本部的到期债务及补充流动资金。</t>
         </is>
       </c>
       <c r="AC85" s="3" t="inlineStr">
         <is>
-          <t>招商银行股份有限公司,中国工商银行股份有限公司</t>
+          <t>招商银行股份有限公司,中国工商银行股份有限公司,中国建设银行股份有限公司,中国银行股份有限公司</t>
         </is>
       </c>
       <c r="AD85" s="3"/>
@@ -19935,7 +19933,7 @@
       </c>
       <c r="AF85" s="3" t="inlineStr">
         <is>
-          <t>外商独资企业</t>
+          <t>中央国有企业</t>
         </is>
       </c>
       <c r="AG85" s="3" t="inlineStr">
@@ -19945,7 +19943,7 @@
       </c>
       <c r="AH85" s="3" t="inlineStr">
         <is>
-          <t>中集安瑞科控股有限公司2026年度第二期超短期融资券</t>
+          <t>招商局集团有限公司2026年度第六期超短期融资券</t>
         </is>
       </c>
       <c r="AI85" s="3" t="inlineStr">
@@ -19979,25 +19977,29 @@
           <t>产业</t>
         </is>
       </c>
-      <c r="AP85" s="3"/>
+      <c r="AP85" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="AQ85" s="3" t="inlineStr">
         <is>
-          <t>其他设备制造</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR85" s="3" t="inlineStr">
         <is>
-          <t>其他专用设备</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS85" s="3" t="inlineStr">
         <is>
-          <t>其他专用设备</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT85" s="3" t="inlineStr">
         <is>
-          <t>石油化工</t>
+          <t>房地产开发</t>
         </is>
       </c>
       <c r="AU85" s="3" t="inlineStr">
@@ -20025,14 +20027,12 @@
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="AZ85" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ85" s="3"/>
     </row>
     <row r="86" customHeight="true" ht="18.0">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>26招商局SCP006</t>
+          <t>26靖江滨江PPN001</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
@@ -20042,64 +20042,64 @@
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>012682292.IB</t>
+          <t>032680528.IB</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E86" s="4" t="n">
-        <v>50.0</v>
+        <v>2.0</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>50.0</v>
+        <v>2.0</v>
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>1.25 ~ 1.65</t>
+          <t>1.38 ~ 2.18</t>
         </is>
       </c>
       <c r="H86" s="4" t="n">
-        <v>1.42</v>
+        <v>1.76</v>
       </c>
       <c r="I86" s="4" t="n">
-        <v>21.33</v>
+        <v>50.21</v>
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="K86" s="3" t="inlineStr">
         <is>
-          <t>26招商局SCP005</t>
+          <t>24靖滨03</t>
         </is>
       </c>
       <c r="L86" s="3" t="inlineStr">
         <is>
-          <t>126D</t>
+          <t>2.93Y</t>
         </is>
       </c>
       <c r="M86" s="3" t="inlineStr">
         <is>
-          <t>1.4800</t>
+          <t>1.7342</t>
         </is>
       </c>
       <c r="N86" s="3" t="inlineStr">
         <is>
-          <t>--/1.4700</t>
+          <t>--/1.7300</t>
         </is>
       </c>
       <c r="O86" s="3" t="inlineStr">
         <is>
-          <t>招商局集团有限公司</t>
+          <t>靖江市滨江新城投资开发有限公司</t>
         </is>
       </c>
       <c r="P86" s="3" t="inlineStr">
         <is>
-          <t>B 54.02</t>
+          <t>C- 23.60</t>
         </is>
       </c>
       <c r="Q86" s="3" t="inlineStr">
@@ -20123,49 +20123,51 @@
         </is>
       </c>
       <c r="U86" s="4" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="V86" s="3"/>
+        <v>3.1</v>
+      </c>
+      <c r="V86" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="W86" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X86" s="3" t="inlineStr">
         <is>
-          <t>1.48%~1.52%</t>
+          <t>1.85%~1.95%</t>
         </is>
       </c>
       <c r="Y86" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z86" s="3"/>
       <c r="AA86" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>江苏省-泰州市</t>
         </is>
       </c>
       <c r="AB86" s="3" t="inlineStr">
         <is>
-          <t>公司此次发行50亿元超短期融资券,募集资金拟用于偿还发行人本部的到期债务及补充流动资金。</t>
+          <t>本期定向债务融资工具发行金额2亿元,置换有息债务[23靖江滨江MTN001]</t>
         </is>
       </c>
       <c r="AC86" s="3" t="inlineStr">
         <is>
-          <t>招商银行股份有限公司,中国工商银行股份有限公司,中国建设银行股份有限公司,中国银行股份有限公司</t>
+          <t>浙商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD86" s="3"/>
       <c r="AE86" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF86" s="3" t="inlineStr">
         <is>
-          <t>中央国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG86" s="3" t="inlineStr">
@@ -20175,17 +20177,17 @@
       </c>
       <c r="AH86" s="3" t="inlineStr">
         <is>
-          <t>招商局集团有限公司2026年度第六期超短期融资券</t>
+          <t>靖江市滨江新城投资开发有限公司2026年度第一期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI86" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ86" s="3" t="inlineStr">
         <is>
-          <t>2027-06-15</t>
+          <t>2029-09-18</t>
         </is>
       </c>
       <c r="AK86" s="3"/>
@@ -20206,32 +20208,32 @@
       </c>
       <c r="AO86" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP86" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ86" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR86" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS86" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT86" s="3" t="inlineStr">
         <is>
-          <t>房地产开发</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU86" s="3" t="inlineStr">
@@ -20259,12 +20261,14 @@
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="AZ86" s="3"/>
+      <c r="AZ86" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="87" customHeight="true" ht="18.0">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>26靖江滨江PPN001</t>
+          <t>26甘国投SCP003</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
@@ -20274,64 +20278,64 @@
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>032680528.IB</t>
+          <t>012682297.IB</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E87" s="4" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="F87" s="4" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>1.38 ~ 2.18</t>
+          <t>1.30 ~ 1.52</t>
         </is>
       </c>
       <c r="H87" s="4" t="n">
-        <v>1.76</v>
+        <v>1.52</v>
       </c>
       <c r="I87" s="4" t="n">
-        <v>50.21</v>
+        <v>31.33</v>
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="K87" s="3" t="inlineStr">
         <is>
-          <t>24靖滨03</t>
+          <t>24甘国投MTN004</t>
         </is>
       </c>
       <c r="L87" s="3" t="inlineStr">
         <is>
-          <t>2.93Y</t>
+          <t>295D</t>
         </is>
       </c>
       <c r="M87" s="3" t="inlineStr">
         <is>
-          <t>1.7342</t>
+          <t>1.5586</t>
         </is>
       </c>
       <c r="N87" s="3" t="inlineStr">
         <is>
-          <t>--/1.7300</t>
+          <t>1.5800/--</t>
         </is>
       </c>
       <c r="O87" s="3" t="inlineStr">
         <is>
-          <t>靖江市滨江新城投资开发有限公司</t>
+          <t>甘肃省国有资产投资集团有限公司</t>
         </is>
       </c>
       <c r="P87" s="3" t="inlineStr">
         <is>
-          <t>C- 23.60</t>
+          <t>C- 20.83</t>
         </is>
       </c>
       <c r="Q87" s="3" t="inlineStr">
@@ -20355,46 +20359,44 @@
         </is>
       </c>
       <c r="U87" s="4" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="V87" s="4" t="n">
-        <v>1.0</v>
-      </c>
+        <v>0.56</v>
+      </c>
+      <c r="V87" s="3"/>
       <c r="W87" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>4-</t>
         </is>
       </c>
       <c r="X87" s="3" t="inlineStr">
         <is>
-          <t>1.85%~1.95%</t>
+          <t>1.53%~1.57%</t>
         </is>
       </c>
       <c r="Y87" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z87" s="3"/>
       <c r="AA87" s="3" t="inlineStr">
         <is>
-          <t>江苏省-泰州市</t>
+          <t>甘肃省</t>
         </is>
       </c>
       <c r="AB87" s="3" t="inlineStr">
         <is>
-          <t>本期定向债务融资工具发行金额2亿元,置换有息债务[23靖江滨江MTN001]</t>
+          <t>发行人本期超短期融资券发行规模为5亿元,拟全部用于偿还发行人有息债务[23甘国投MTN002]</t>
         </is>
       </c>
       <c r="AC87" s="3" t="inlineStr">
         <is>
-          <t>浙商银行股份有限公司</t>
+          <t>上海浦东发展银行股份有限公司</t>
         </is>
       </c>
       <c r="AD87" s="3"/>
       <c r="AE87" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF87" s="3" t="inlineStr">
@@ -20409,17 +20411,17 @@
       </c>
       <c r="AH87" s="3" t="inlineStr">
         <is>
-          <t>靖江市滨江新城投资开发有限公司2026年度第一期定向债务融资工具</t>
+          <t>甘肃省国有资产投资集团有限公司2026年度第三期超短期融资券</t>
         </is>
       </c>
       <c r="AI87" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ87" s="3" t="inlineStr">
         <is>
-          <t>2029-09-18</t>
+          <t>2027-06-15</t>
         </is>
       </c>
       <c r="AK87" s="3"/>
@@ -20440,32 +20442,32 @@
       </c>
       <c r="AO87" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP87" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ87" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR87" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS87" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT87" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>工业金属</t>
         </is>
       </c>
       <c r="AU87" s="3" t="inlineStr">
@@ -20493,14 +20495,12 @@
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="AZ87" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ87" s="3"/>
     </row>
     <row r="88" customHeight="true" ht="18.0">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>26甘国投SCP003</t>
+          <t>26沈平国资MTN001</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
@@ -20510,64 +20510,64 @@
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>012682297.IB</t>
+          <t>102683700.IB</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E88" s="4" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.52</t>
+          <t>1.80 ~ 3.00</t>
         </is>
       </c>
       <c r="H88" s="4" t="n">
-        <v>1.52</v>
+        <v>2.23</v>
       </c>
       <c r="I88" s="4" t="n">
-        <v>31.33</v>
+        <v>81.94</v>
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="K88" s="3" t="inlineStr">
         <is>
-          <t>24甘国投MTN004</t>
+          <t>24沈平国资PPN001</t>
         </is>
       </c>
       <c r="L88" s="3" t="inlineStr">
         <is>
-          <t>295D</t>
+          <t>2.51Y</t>
         </is>
       </c>
       <c r="M88" s="3" t="inlineStr">
         <is>
-          <t>1.5586</t>
+          <t>1.9022</t>
         </is>
       </c>
       <c r="N88" s="3" t="inlineStr">
         <is>
-          <t>1.5800/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O88" s="3" t="inlineStr">
         <is>
-          <t>甘肃省国有资产投资集团有限公司</t>
+          <t>沈阳市和平区国有资产经营有限公司</t>
         </is>
       </c>
       <c r="P88" s="3" t="inlineStr">
         <is>
-          <t>C- 20.83</t>
+          <t>C- 24.37</t>
         </is>
       </c>
       <c r="Q88" s="3" t="inlineStr">
@@ -20577,7 +20577,7 @@
       </c>
       <c r="R88" s="3" t="inlineStr">
         <is>
-          <t>09-17 09:00</t>
+          <t>09-17 10:00</t>
         </is>
       </c>
       <c r="S88" s="3" t="inlineStr">
@@ -20591,44 +20591,46 @@
         </is>
       </c>
       <c r="U88" s="4" t="n">
-        <v>0.56</v>
-      </c>
-      <c r="V88" s="3"/>
+        <v>2.6</v>
+      </c>
+      <c r="V88" s="4" t="n">
+        <v>2.33</v>
+      </c>
       <c r="W88" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X88" s="3" t="inlineStr">
         <is>
-          <t>1.53%~1.57%</t>
+          <t>1.90%~2.00%</t>
         </is>
       </c>
       <c r="Y88" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z88" s="3"/>
       <c r="AA88" s="3" t="inlineStr">
         <is>
-          <t>甘肃省</t>
+          <t>辽宁省-沈阳市</t>
         </is>
       </c>
       <c r="AB88" s="3" t="inlineStr">
         <is>
-          <t>发行人本期超短期融资券发行规模为5亿元,拟全部用于偿还发行人有息债务[23甘国投MTN002]</t>
+          <t>本期中期票据发行金额3.00亿元,拟全部用于偿还公司存续债务融资工具本金。[23沈平国资PPN001]</t>
         </is>
       </c>
       <c r="AC88" s="3" t="inlineStr">
         <is>
-          <t>上海浦东发展银行股份有限公司</t>
+          <t>光大证券股份有限公司,中信建投证券股份有限公司</t>
         </is>
       </c>
       <c r="AD88" s="3"/>
       <c r="AE88" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF88" s="3" t="inlineStr">
@@ -20643,7 +20645,7 @@
       </c>
       <c r="AH88" s="3" t="inlineStr">
         <is>
-          <t>甘肃省国有资产投资集团有限公司2026年度第三期超短期融资券</t>
+          <t>沈阳市和平区国有资产经营有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI88" s="3" t="inlineStr">
@@ -20653,7 +20655,7 @@
       </c>
       <c r="AJ88" s="3" t="inlineStr">
         <is>
-          <t>2027-06-15</t>
+          <t>2031-09-18</t>
         </is>
       </c>
       <c r="AK88" s="3"/>
@@ -20674,12 +20676,12 @@
       </c>
       <c r="AO88" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP88" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ88" s="3" t="inlineStr">
@@ -20689,17 +20691,17 @@
       </c>
       <c r="AR88" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS88" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT88" s="3" t="inlineStr">
         <is>
-          <t>工业金属</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU88" s="3" t="inlineStr">
@@ -20727,12 +20729,14 @@
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="AZ88" s="3"/>
+      <c r="AZ88" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="89" customHeight="true" ht="18.0">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>26沈平国资MTN001</t>
+          <t>26沛县城建MTN001</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
@@ -20742,7 +20746,7 @@
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>102683700.IB</t>
+          <t>102683702.IB</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
@@ -20751,40 +20755,40 @@
         </is>
       </c>
       <c r="E89" s="4" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 3.00</t>
+          <t>1.70 ~ 2.20</t>
         </is>
       </c>
       <c r="H89" s="4" t="n">
-        <v>2.23</v>
+        <v>1.86</v>
       </c>
       <c r="I89" s="4" t="n">
-        <v>81.94</v>
+        <v>44.94</v>
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="K89" s="3" t="inlineStr">
         <is>
-          <t>24沈平国资PPN001</t>
+          <t>26沛城01</t>
         </is>
       </c>
       <c r="L89" s="3" t="inlineStr">
         <is>
-          <t>2.51Y</t>
+          <t>4.58Y</t>
         </is>
       </c>
       <c r="M89" s="3" t="inlineStr">
         <is>
-          <t>1.9022</t>
+          <t>1.8796</t>
         </is>
       </c>
       <c r="N89" s="3" t="inlineStr">
@@ -20794,12 +20798,12 @@
       </c>
       <c r="O89" s="3" t="inlineStr">
         <is>
-          <t>沈阳市和平区国有资产经营有限公司</t>
+          <t>沛县城市建设投资发展集团有限公司</t>
         </is>
       </c>
       <c r="P89" s="3" t="inlineStr">
         <is>
-          <t>C- 24.37</t>
+          <t>D 4.76</t>
         </is>
       </c>
       <c r="Q89" s="3" t="inlineStr">
@@ -20809,7 +20813,7 @@
       </c>
       <c r="R89" s="3" t="inlineStr">
         <is>
-          <t>09-17 10:00</t>
+          <t>09-17 14:00</t>
         </is>
       </c>
       <c r="S89" s="3" t="inlineStr">
@@ -20823,10 +20827,10 @@
         </is>
       </c>
       <c r="U89" s="4" t="n">
-        <v>2.6</v>
+        <v>4.1</v>
       </c>
       <c r="V89" s="4" t="n">
-        <v>2.33</v>
+        <v>5.5</v>
       </c>
       <c r="W89" s="3" t="inlineStr">
         <is>
@@ -20835,7 +20839,7 @@
       </c>
       <c r="X89" s="3" t="inlineStr">
         <is>
-          <t>1.90%~2.00%</t>
+          <t>1.89%~1.99%</t>
         </is>
       </c>
       <c r="Y89" s="3" t="inlineStr">
@@ -20846,17 +20850,17 @@
       <c r="Z89" s="3"/>
       <c r="AA89" s="3" t="inlineStr">
         <is>
-          <t>辽宁省-沈阳市</t>
+          <t>江苏省-徐州市</t>
         </is>
       </c>
       <c r="AB89" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行金额3.00亿元,拟全部用于偿还公司存续债务融资工具本金。[23沈平国资PPN001]</t>
+          <t>本次中期票据拟发行金额为5亿元，本期中期票据募集资金拟用于偿还接续“23沛县城建MTN001”的专项过桥贷款</t>
         </is>
       </c>
       <c r="AC89" s="3" t="inlineStr">
         <is>
-          <t>光大证券股份有限公司,中信建投证券股份有限公司</t>
+          <t>中国光大银行股份有限公司,江苏银行股份有限公司</t>
         </is>
       </c>
       <c r="AD89" s="3"/>
@@ -20877,7 +20881,7 @@
       </c>
       <c r="AH89" s="3" t="inlineStr">
         <is>
-          <t>沈阳市和平区国有资产经营有限公司2026年度第一期中期票据</t>
+          <t>沛县城市建设投资发展集团有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI89" s="3" t="inlineStr">
@@ -20913,22 +20917,22 @@
       </c>
       <c r="AP89" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ89" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR89" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS89" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT89" s="3" t="inlineStr">
@@ -20968,74 +20972,74 @@
     <row r="90" customHeight="true" ht="18.0">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>26沛县城建MTN001</t>
+          <t>26TCL实业MTN001(两新科创债)</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>09-17 18:00</t>
+          <t>09-18 18:00</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>102683702.IB</t>
+          <t>102683715.IB</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E90" s="4" t="n">
-        <v>5.0</v>
+        <v>15.0</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v>5.0</v>
+        <v>15.0</v>
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.20</t>
+          <t>1.70 ~ 2.00</t>
         </is>
       </c>
       <c r="H90" s="4" t="n">
-        <v>1.86</v>
+        <v>1.78</v>
       </c>
       <c r="I90" s="4" t="n">
-        <v>44.94</v>
+        <v>51.41</v>
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="K90" s="3" t="inlineStr">
         <is>
-          <t>26沛城01</t>
+          <t>26TCL实业SCP002(绿色两新)</t>
         </is>
       </c>
       <c r="L90" s="3" t="inlineStr">
         <is>
-          <t>4.58Y</t>
+          <t>78D</t>
         </is>
       </c>
       <c r="M90" s="3" t="inlineStr">
         <is>
-          <t>1.8796</t>
+          <t>1.5100</t>
         </is>
       </c>
       <c r="N90" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5300/--</t>
         </is>
       </c>
       <c r="O90" s="3" t="inlineStr">
         <is>
-          <t>沛县城市建设投资发展集团有限公司</t>
+          <t>TCL实业控股股份有限公司</t>
         </is>
       </c>
       <c r="P90" s="3" t="inlineStr">
         <is>
-          <t>D 4.76</t>
+          <t>D+ 5.71</t>
         </is>
       </c>
       <c r="Q90" s="3" t="inlineStr">
@@ -21045,7 +21049,7 @@
       </c>
       <c r="R90" s="3" t="inlineStr">
         <is>
-          <t>09-17 14:00</t>
+          <t>09-17 09:00</t>
         </is>
       </c>
       <c r="S90" s="3" t="inlineStr">
@@ -21055,44 +21059,44 @@
       </c>
       <c r="T90" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="U90" s="4" t="n">
-        <v>4.1</v>
+        <v>4.1267</v>
       </c>
       <c r="V90" s="4" t="n">
-        <v>5.5</v>
+        <v>1.06</v>
       </c>
       <c r="W90" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X90" s="3" t="inlineStr">
         <is>
-          <t>1.89%~1.99%</t>
+          <t>1.62%~1.72%</t>
         </is>
       </c>
       <c r="Y90" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3" t="inlineStr">
         <is>
-          <t>江苏省-徐州市</t>
+          <t>广东省-惠州市</t>
         </is>
       </c>
       <c r="AB90" s="3" t="inlineStr">
         <is>
-          <t>本次中期票据拟发行金额为5亿元，本期中期票据募集资金拟用于偿还接续“23沛县城建MTN001”的专项过桥贷款</t>
+          <t>发行人本期中期票据发行规模15亿元,本期债券募集资金计划全部用于置换发行人近三个月用于高效节能低碳电器设备制造类项目的原材料采购的自有资金支出,同时,本期绿色两新科技创新债券募集资金不低于30%用于“两新”领域</t>
         </is>
       </c>
       <c r="AC90" s="3" t="inlineStr">
         <is>
-          <t>中国光大银行股份有限公司,江苏银行股份有限公司</t>
+          <t>中国工商银行股份有限公司,中国农业银行股份有限公司,中国建设银行股份有限公司,中信银行股份有限公司</t>
         </is>
       </c>
       <c r="AD90" s="3"/>
@@ -21103,7 +21107,7 @@
       </c>
       <c r="AF90" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>民营企业</t>
         </is>
       </c>
       <c r="AG90" s="3" t="inlineStr">
@@ -21113,7 +21117,7 @@
       </c>
       <c r="AH90" s="3" t="inlineStr">
         <is>
-          <t>沛县城市建设投资发展集团有限公司2026年度第一期中期票据</t>
+          <t>TCL实业控股股份有限公司2026年度第一期绿色两新科技创新债券</t>
         </is>
       </c>
       <c r="AI90" s="3" t="inlineStr">
@@ -21123,13 +21127,13 @@
       </c>
       <c r="AJ90" s="3" t="inlineStr">
         <is>
-          <t>2031-09-18</t>
+          <t>2029-09-21</t>
         </is>
       </c>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AM90" s="3" t="inlineStr">
@@ -21139,62 +21143,62 @@
       </c>
       <c r="AN90" s="3" t="inlineStr">
         <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="AO90" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP90" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AQ90" s="3" t="inlineStr">
+        <is>
+          <t>电子设备制造</t>
+        </is>
+      </c>
+      <c r="AR90" s="3" t="inlineStr">
+        <is>
+          <t>家用电器</t>
+        </is>
+      </c>
+      <c r="AS90" s="3" t="inlineStr">
+        <is>
+          <t>家用电器</t>
+        </is>
+      </c>
+      <c r="AT90" s="3" t="inlineStr">
+        <is>
+          <t>视听器材</t>
+        </is>
+      </c>
+      <c r="AU90" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV90" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW90" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AX90" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY90" s="3" t="inlineStr">
+        <is>
           <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="AO90" s="3" t="inlineStr">
-        <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP90" s="3" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="AQ90" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR90" s="3" t="inlineStr">
-        <is>
-          <t>城市基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AS90" s="3" t="inlineStr">
-        <is>
-          <t>城市基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AT90" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AU90" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AV90" s="3" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AW90" s="3" t="inlineStr">
-        <is>
-          <t>不含权</t>
-        </is>
-      </c>
-      <c r="AX90" s="3" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AY90" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AZ90" s="4" t="n">
@@ -21204,22 +21208,22 @@
     <row r="91" customHeight="true" ht="18.0">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>26TCL实业MTN001(两新科创债)</t>
+          <t>26深能Y5</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>09-18 18:00</t>
+          <t>09-17 19:00</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>102683715.IB</t>
+          <t>525020.SZ</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E91" s="4" t="n">
@@ -21230,48 +21234,48 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.00</t>
+          <t>1.30 ~ 2.10</t>
         </is>
       </c>
       <c r="H91" s="4" t="n">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="I91" s="4" t="n">
-        <v>51.41</v>
+        <v>45.21</v>
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="K91" s="3" t="inlineStr">
         <is>
-          <t>26TCL实业SCP002(绿色两新)</t>
+          <t>26深能Y4</t>
         </is>
       </c>
       <c r="L91" s="3" t="inlineStr">
         <is>
-          <t>78D</t>
+          <t>2.96Y+N</t>
         </is>
       </c>
       <c r="M91" s="3" t="inlineStr">
         <is>
-          <t>1.5100</t>
+          <t>1.7096</t>
         </is>
       </c>
       <c r="N91" s="3" t="inlineStr">
         <is>
-          <t>1.5300/--</t>
+          <t>1.7100/1.6900</t>
         </is>
       </c>
       <c r="O91" s="3" t="inlineStr">
         <is>
-          <t>TCL实业控股股份有限公司</t>
+          <t>深圳能源集团股份有限公司</t>
         </is>
       </c>
       <c r="P91" s="3" t="inlineStr">
         <is>
-          <t>D+ 5.71</t>
+          <t>B- 41.04</t>
         </is>
       </c>
       <c r="Q91" s="3" t="inlineStr">
@@ -21281,7 +21285,7 @@
       </c>
       <c r="R91" s="3" t="inlineStr">
         <is>
-          <t>09-17 09:00</t>
+          <t>09-17 15:00</t>
         </is>
       </c>
       <c r="S91" s="3" t="inlineStr">
@@ -21295,19 +21299,17 @@
         </is>
       </c>
       <c r="U91" s="4" t="n">
-        <v>4.1267</v>
-      </c>
-      <c r="V91" s="4" t="n">
-        <v>1.06</v>
-      </c>
+        <v>2.91</v>
+      </c>
+      <c r="V91" s="3"/>
       <c r="W91" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X91" s="3" t="inlineStr">
         <is>
-          <t>1.62%~1.72%</t>
+          <t>1.67%~1.77%</t>
         </is>
       </c>
       <c r="Y91" s="3" t="inlineStr">
@@ -21315,41 +21317,45 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z91" s="3"/>
+      <c r="Z91" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA91" s="3" t="inlineStr">
         <is>
-          <t>广东省-惠州市</t>
+          <t>广东省-深圳市</t>
         </is>
       </c>
       <c r="AB91" s="3" t="inlineStr">
         <is>
-          <t>发行人本期中期票据发行规模15亿元,本期债券募集资金计划全部用于置换发行人近三个月用于高效节能低碳电器设备制造类项目的原材料采购的自有资金支出,同时,本期绿色两新科技创新债券募集资金不低于30%用于“两新”领域</t>
+          <t>本期债券的募集资金在扣除发行费用后,拟用于偿还到期债务。[23深能源MTN002]</t>
         </is>
       </c>
       <c r="AC91" s="3" t="inlineStr">
         <is>
-          <t>中国工商银行股份有限公司,中国农业银行股份有限公司,中国建设银行股份有限公司,中信银行股份有限公司</t>
+          <t>中国国际金融股份有限公司,国泰海通证券股份有限公司,中信证券股份有限公司,招商证券股份有限公司,国信证券股份有限公司,广发证券股份有限公司</t>
         </is>
       </c>
       <c r="AD91" s="3"/>
       <c r="AE91" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF91" s="3" t="inlineStr">
         <is>
-          <t>民营企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG91" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH91" s="3" t="inlineStr">
         <is>
-          <t>TCL实业控股股份有限公司2026年度第一期绿色两新科技创新债券</t>
+          <t>深圳能源集团股份有限公司2026年面向专业投资者公开发行可续期公司债券(第五期)</t>
         </is>
       </c>
       <c r="AI91" s="3" t="inlineStr">
@@ -21365,7 +21371,7 @@
       <c r="AK91" s="3"/>
       <c r="AL91" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t/>
         </is>
       </c>
       <c r="AM91" s="3" t="inlineStr">
@@ -21385,27 +21391,27 @@
       </c>
       <c r="AP91" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AQ91" s="3" t="inlineStr">
         <is>
-          <t>电子设备制造</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR91" s="3" t="inlineStr">
         <is>
-          <t>家用电器</t>
+          <t>综合公用</t>
         </is>
       </c>
       <c r="AS91" s="3" t="inlineStr">
         <is>
-          <t>家用电器</t>
+          <t>综合公用</t>
         </is>
       </c>
       <c r="AT91" s="3" t="inlineStr">
         <is>
-          <t>视听器材</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AU91" s="3" t="inlineStr">
@@ -21420,94 +21426,92 @@
       </c>
       <c r="AW91" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX91" s="3" t="inlineStr">
         <is>
-          <t>普通债权</t>
+          <t>次级债权</t>
         </is>
       </c>
       <c r="AY91" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="AZ91" s="4" t="n">
-        <v>0.01</v>
-      </c>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="AZ91" s="3"/>
     </row>
     <row r="92" customHeight="true" ht="18.0">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>26深能Y5</t>
+          <t>26电建租赁SCP002</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>09-17 19:00</t>
+          <t>09-18 18:00</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>525020.SZ</t>
+          <t>012682301.IB</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>0.23Y</t>
         </is>
       </c>
       <c r="E92" s="4" t="n">
-        <v>15.0</v>
+        <v>5.0</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v>15.0</v>
+        <v>5.0</v>
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.10</t>
+          <t>1.20 ~ 2.20</t>
         </is>
       </c>
       <c r="H92" s="4" t="n">
-        <v>1.71</v>
+        <v>1.54</v>
       </c>
       <c r="I92" s="4" t="n">
-        <v>45.21</v>
+        <v>36.0</v>
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="K92" s="3" t="inlineStr">
         <is>
-          <t>26深能Y4</t>
+          <t>24电租Y1</t>
         </is>
       </c>
       <c r="L92" s="3" t="inlineStr">
         <is>
-          <t>2.96Y+N</t>
+          <t>76D+N</t>
         </is>
       </c>
       <c r="M92" s="3" t="inlineStr">
         <is>
-          <t>1.7096</t>
+          <t>1.9115</t>
         </is>
       </c>
       <c r="N92" s="3" t="inlineStr">
         <is>
-          <t>1.7100/1.6900</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O92" s="3" t="inlineStr">
         <is>
-          <t>深圳能源集团股份有限公司</t>
+          <t>中国电建集团租赁有限公司</t>
         </is>
       </c>
       <c r="P92" s="3" t="inlineStr">
         <is>
-          <t>B- 41.04</t>
+          <t>D+ 6.87</t>
         </is>
       </c>
       <c r="Q92" s="3" t="inlineStr">
@@ -21517,7 +21521,7 @@
       </c>
       <c r="R92" s="3" t="inlineStr">
         <is>
-          <t>09-17 15:00</t>
+          <t>09-17 09:00</t>
         </is>
       </c>
       <c r="S92" s="3" t="inlineStr">
@@ -21531,63 +21535,59 @@
         </is>
       </c>
       <c r="U92" s="4" t="n">
-        <v>2.91</v>
+        <v>3.16</v>
       </c>
       <c r="V92" s="3"/>
       <c r="W92" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X92" s="3" t="inlineStr">
         <is>
-          <t>1.67%~1.77%</t>
+          <t>1.59%~1.63%</t>
         </is>
       </c>
       <c r="Y92" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z92" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z92" s="3"/>
       <c r="AA92" s="3" t="inlineStr">
         <is>
-          <t>广东省-深圳市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB92" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金在扣除发行费用后,拟用于偿还到期债务。[23深能源MTN002]</t>
+          <t>本期债务融资工具发行金额为5.00亿元,拟用于偿还到期债务融资工具[26电建租赁SCP001]</t>
         </is>
       </c>
       <c r="AC92" s="3" t="inlineStr">
         <is>
-          <t>中国国际金融股份有限公司,国泰海通证券股份有限公司,中信证券股份有限公司,招商证券股份有限公司,国信证券股份有限公司,广发证券股份有限公司</t>
+          <t>宁波银行股份有限公司</t>
         </is>
       </c>
       <c r="AD92" s="3"/>
       <c r="AE92" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF92" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG92" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH92" s="3" t="inlineStr">
         <is>
-          <t>深圳能源集团股份有限公司2026年面向专业投资者公开发行可续期公司债券(第五期)</t>
+          <t>中国电建集团租赁有限公司2026年度第二期超短期融资券</t>
         </is>
       </c>
       <c r="AI92" s="3" t="inlineStr">
@@ -21597,60 +21597,60 @@
       </c>
       <c r="AJ92" s="3" t="inlineStr">
         <is>
-          <t>2029-09-21</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="AK92" s="3"/>
       <c r="AL92" s="3" t="inlineStr">
         <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AM92" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AN92" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="AO92" s="3" t="inlineStr">
+        <is>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP92" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AQ92" s="3" t="inlineStr">
+        <is>
+          <t>非银</t>
+        </is>
+      </c>
+      <c r="AR92" s="3" t="inlineStr">
+        <is>
+          <t>融资租赁</t>
+        </is>
+      </c>
+      <c r="AS92" s="3" t="inlineStr">
+        <is>
+          <t>融资租赁</t>
+        </is>
+      </c>
+      <c r="AT92" s="3" t="inlineStr">
+        <is>
+          <t>多元金融</t>
+        </is>
+      </c>
+      <c r="AU92" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM92" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="AN92" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="AO92" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP92" s="3" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
-      <c r="AQ92" s="3" t="inlineStr">
-        <is>
-          <t>公用事业</t>
-        </is>
-      </c>
-      <c r="AR92" s="3" t="inlineStr">
-        <is>
-          <t>综合公用</t>
-        </is>
-      </c>
-      <c r="AS92" s="3" t="inlineStr">
-        <is>
-          <t>综合公用</t>
-        </is>
-      </c>
-      <c r="AT92" s="3" t="inlineStr">
-        <is>
-          <t>电力</t>
-        </is>
-      </c>
-      <c r="AU92" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV92" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -21658,92 +21658,94 @@
       </c>
       <c r="AW92" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX92" s="3" t="inlineStr">
         <is>
-          <t>次级债权</t>
+          <t>普通债权</t>
         </is>
       </c>
       <c r="AY92" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="AZ92" s="3"/>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="AZ92" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="93" customHeight="true" ht="18.0">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>26电建租赁SCP002</t>
+          <t>26招证S5</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>09-18 18:00</t>
+          <t>09-17 19:00</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>012682301.IB</t>
+          <t>246111.SH</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>0.23Y</t>
+          <t>0.91Y</t>
         </is>
       </c>
       <c r="E93" s="4" t="n">
-        <v>5.0</v>
+        <v>50.0</v>
       </c>
       <c r="F93" s="4" t="n">
-        <v>5.0</v>
+        <v>80.0</v>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
+          <t>1.00 ~ 2.00</t>
         </is>
       </c>
       <c r="H93" s="4" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="I93" s="4" t="n">
-        <v>36.0</v>
+        <v>30.1</v>
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="K93" s="3" t="inlineStr">
         <is>
-          <t>24电租Y1</t>
+          <t>26招证S3</t>
         </is>
       </c>
       <c r="L93" s="3" t="inlineStr">
         <is>
-          <t>76D+N</t>
+          <t>294D</t>
         </is>
       </c>
       <c r="M93" s="3" t="inlineStr">
         <is>
-          <t>1.9115</t>
+          <t>1.4504</t>
         </is>
       </c>
       <c r="N93" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5300/1.5100</t>
         </is>
       </c>
       <c r="O93" s="3" t="inlineStr">
         <is>
-          <t>中国电建集团租赁有限公司</t>
+          <t>招商证券股份有限公司</t>
         </is>
       </c>
       <c r="P93" s="3" t="inlineStr">
         <is>
-          <t>D+ 6.87</t>
+          <t>B 54.27</t>
         </is>
       </c>
       <c r="Q93" s="3" t="inlineStr">
@@ -21753,7 +21755,7 @@
       </c>
       <c r="R93" s="3" t="inlineStr">
         <is>
-          <t>09-17 09:00</t>
+          <t>09-17 15:00</t>
         </is>
       </c>
       <c r="S93" s="3" t="inlineStr">
@@ -21767,44 +21769,44 @@
         </is>
       </c>
       <c r="U93" s="4" t="n">
-        <v>3.16</v>
+        <v>2.07</v>
       </c>
       <c r="V93" s="3"/>
       <c r="W93" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="X93" s="3" t="inlineStr">
         <is>
-          <t>1.59%~1.63%</t>
+          <t>1.47%~1.51%</t>
         </is>
       </c>
       <c r="Y93" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z93" s="3"/>
       <c r="AA93" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>广东省-深圳市</t>
         </is>
       </c>
       <c r="AB93" s="3" t="inlineStr">
         <is>
-          <t>本期债务融资工具发行金额为5.00亿元,拟用于偿还到期债务融资工具[26电建租赁SCP001]</t>
+          <t>本期债券募集资金将用于满足公司业务运营需要，调整公司债务结构，偿还到期债务，补充公司流动资金。其中拟将不超过85亿元（含85亿元）用于偿还到期公司债券本金，不超过15亿元（含15亿元）用于补充公司流动资金</t>
         </is>
       </c>
       <c r="AC93" s="3" t="inlineStr">
         <is>
-          <t>宁波银行股份有限公司</t>
+          <t>华泰联合证券有限责任公司,国泰海通证券股份有限公司,申万宏源证券有限公司</t>
         </is>
       </c>
       <c r="AD93" s="3"/>
       <c r="AE93" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>证券公司债</t>
         </is>
       </c>
       <c r="AF93" s="3" t="inlineStr">
@@ -21814,12 +21816,12 @@
       </c>
       <c r="AG93" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH93" s="3" t="inlineStr">
         <is>
-          <t>中国电建集团租赁有限公司2026年度第二期超短期融资券</t>
+          <t>招商证券股份有限公司2026年面向专业投资者公开发行短期公司债券(第三期)(品种二)</t>
         </is>
       </c>
       <c r="AI93" s="3" t="inlineStr">
@@ -21829,13 +21831,13 @@
       </c>
       <c r="AJ93" s="3" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2027-08-19</t>
         </is>
       </c>
       <c r="AK93" s="3"/>
       <c r="AL93" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t/>
         </is>
       </c>
       <c r="AM93" s="3" t="inlineStr">
@@ -21855,7 +21857,7 @@
       </c>
       <c r="AP93" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AQ93" s="3" t="inlineStr">
@@ -21865,17 +21867,17 @@
       </c>
       <c r="AR93" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AS93" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>券商</t>
         </is>
       </c>
       <c r="AT93" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AU93" s="3" t="inlineStr">
@@ -21900,84 +21902,82 @@
       </c>
       <c r="AY93" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="AZ93" s="4" t="n">
-        <v>0.01</v>
-      </c>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="AZ93" s="3"/>
     </row>
     <row r="94" customHeight="true" ht="18.0">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>26招证S5</t>
+          <t>26广州银行二级资本债01</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>09-17 19:00</t>
+          <t>09-17 18:00</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>246111.SH</t>
+          <t>232680037.IB</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>0.91Y</t>
+          <t>5+5</t>
         </is>
       </c>
       <c r="E94" s="4" t="n">
-        <v>50.0</v>
+        <v>20.0</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v>80.0</v>
+        <v>40.0</v>
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>1.00 ~ 2.00</t>
+          <t>1.60 ~ 2.20</t>
         </is>
       </c>
       <c r="H94" s="4" t="n">
-        <v>1.52</v>
+        <v>1.87</v>
       </c>
       <c r="I94" s="4" t="n">
-        <v>30.1</v>
+        <v>18.38</v>
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="K94" s="3" t="inlineStr">
         <is>
-          <t>26招证S3</t>
+          <t>22广州银行二级资本债01</t>
         </is>
       </c>
       <c r="L94" s="3" t="inlineStr">
         <is>
-          <t>294D</t>
+          <t>1.28Y+5.00Y</t>
         </is>
       </c>
       <c r="M94" s="3" t="inlineStr">
         <is>
-          <t>1.4504</t>
+          <t>1.5494</t>
         </is>
       </c>
       <c r="N94" s="3" t="inlineStr">
         <is>
-          <t>1.5300/1.5100</t>
+          <t>1.5400/--</t>
         </is>
       </c>
       <c r="O94" s="3" t="inlineStr">
         <is>
-          <t>招商证券股份有限公司</t>
+          <t>广州银行股份有限公司</t>
         </is>
       </c>
       <c r="P94" s="3" t="inlineStr">
         <is>
-          <t>B 54.27</t>
+          <t>A 70.33</t>
         </is>
       </c>
       <c r="Q94" s="3" t="inlineStr">
@@ -21987,7 +21987,7 @@
       </c>
       <c r="R94" s="3" t="inlineStr">
         <is>
-          <t>09-17 15:00</t>
+          <t>09-17 09:00</t>
         </is>
       </c>
       <c r="S94" s="3" t="inlineStr">
@@ -22001,17 +22001,17 @@
         </is>
       </c>
       <c r="U94" s="4" t="n">
-        <v>2.07</v>
+        <v>1.8</v>
       </c>
       <c r="V94" s="3"/>
       <c r="W94" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4-</t>
         </is>
       </c>
       <c r="X94" s="3" t="inlineStr">
         <is>
-          <t>1.47%~1.51%</t>
+          <t>1.83%~1.93%</t>
         </is>
       </c>
       <c r="Y94" s="3" t="inlineStr">
@@ -22019,41 +22019,45 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z94" s="3"/>
+      <c r="Z94" s="3" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
       <c r="AA94" s="3" t="inlineStr">
         <is>
-          <t>广东省-深圳市</t>
+          <t>广东省-广州市</t>
         </is>
       </c>
       <c r="AB94" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金将用于满足公司业务运营需要，调整公司债务结构，偿还到期债务，补充公司流动资金。其中拟将不超过85亿元（含85亿元）用于偿还到期公司债券本金，不超过15亿元（含15亿元）用于补充公司流动资金</t>
+          <t>本期债券发行的募集资金在扣除发行费用后,将依据适用法律和主管部门的批准全部用于补充发行人二级资本。</t>
         </is>
       </c>
       <c r="AC94" s="3" t="inlineStr">
         <is>
-          <t>华泰联合证券有限责任公司,国泰海通证券股份有限公司,申万宏源证券有限公司</t>
+          <t>华泰联合证券有限责任公司,渤海银行股份有限公司,中国工商银行股份有限公司,华夏银行股份有限公司,中国邮政储蓄银行股份有限公司,恒丰银行股份有限公司,中国银行股份有限公司,招商证券股份有限公司,国泰海通证券股份有限公司,国开证券股份有限公司,广发证券股份有限公司</t>
         </is>
       </c>
       <c r="AD94" s="3"/>
       <c r="AE94" s="3" t="inlineStr">
         <is>
-          <t>证券公司债</t>
+          <t>二级资本工具</t>
         </is>
       </c>
       <c r="AF94" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG94" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH94" s="3" t="inlineStr">
         <is>
-          <t>招商证券股份有限公司2026年面向专业投资者公开发行短期公司债券(第三期)(品种二)</t>
+          <t>广州银行股份有限公司2026年二级资本债券(第一期)</t>
         </is>
       </c>
       <c r="AI94" s="3" t="inlineStr">
@@ -22063,18 +22067,22 @@
       </c>
       <c r="AJ94" s="3" t="inlineStr">
         <is>
-          <t>2027-08-19</t>
-        </is>
-      </c>
-      <c r="AK94" s="3"/>
+          <t>2036-09-21</t>
+        </is>
+      </c>
+      <c r="AK94" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL94" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AM94" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AN94" s="3" t="inlineStr">
@@ -22089,32 +22097,32 @@
       </c>
       <c r="AP94" s="3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ94" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AR94" s="3" t="inlineStr">
         <is>
-          <t>证券</t>
+          <t>商业银行</t>
         </is>
       </c>
       <c r="AS94" s="3" t="inlineStr">
         <is>
-          <t>券商</t>
+          <t>城商行</t>
         </is>
       </c>
       <c r="AT94" s="3" t="inlineStr">
         <is>
-          <t>证券</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AU94" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2031-09-21</t>
         </is>
       </c>
       <c r="AV94" s="3" t="inlineStr">
@@ -22124,12 +22132,12 @@
       </c>
       <c r="AW94" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX94" s="3" t="inlineStr">
         <is>
-          <t>普通债权</t>
+          <t>二级资本工具</t>
         </is>
       </c>
       <c r="AY94" s="3" t="inlineStr">
@@ -22142,7 +22150,7 @@
     <row r="95" customHeight="true" ht="18.0">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>26广州银行二级资本债01</t>
+          <t>26中原银行永续债01</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
@@ -22152,64 +22160,64 @@
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>232680037.IB</t>
+          <t>242680047.IB</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>5+5</t>
+          <t>5+N</t>
         </is>
       </c>
       <c r="E95" s="4" t="n">
-        <v>20.0</v>
+        <v>100.0</v>
       </c>
       <c r="F95" s="4" t="n">
-        <v>40.0</v>
+        <v>100.0</v>
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.20</t>
+          <t>1.80 ~ 2.30</t>
         </is>
       </c>
       <c r="H95" s="4" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="I95" s="4" t="n">
-        <v>18.38</v>
+        <v>50.94</v>
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="K95" s="3" t="inlineStr">
         <is>
-          <t>22广州银行二级资本债01</t>
+          <t>23中原银行永续债01</t>
         </is>
       </c>
       <c r="L95" s="3" t="inlineStr">
         <is>
-          <t>1.28Y+5.00Y</t>
+          <t>1.92Y+N</t>
         </is>
       </c>
       <c r="M95" s="3" t="inlineStr">
         <is>
-          <t>1.5494</t>
+          <t>1.6755</t>
         </is>
       </c>
       <c r="N95" s="3" t="inlineStr">
         <is>
-          <t>1.5400/--</t>
+          <t>1.6600/--</t>
         </is>
       </c>
       <c r="O95" s="3" t="inlineStr">
         <is>
-          <t>广州银行股份有限公司</t>
+          <t>中原银行股份有限公司</t>
         </is>
       </c>
       <c r="P95" s="3" t="inlineStr">
         <is>
-          <t>A 70.33</t>
+          <t>B 51.97</t>
         </is>
       </c>
       <c r="Q95" s="3" t="inlineStr">
@@ -22232,9 +22240,7 @@
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="U95" s="4" t="n">
-        <v>1.8</v>
-      </c>
+      <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3" t="inlineStr">
         <is>
@@ -22243,7 +22249,7 @@
       </c>
       <c r="X95" s="3" t="inlineStr">
         <is>
-          <t>1.83%~1.93%</t>
+          <t>1.88%~1.98%</t>
         </is>
       </c>
       <c r="Y95" s="3" t="inlineStr">
@@ -22253,28 +22259,28 @@
       </c>
       <c r="Z95" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="AA95" s="3" t="inlineStr">
         <is>
-          <t>广东省-广州市</t>
+          <t>河南省-郑州市</t>
         </is>
       </c>
       <c r="AB95" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行的募集资金在扣除发行费用后,将依据适用法律和主管部门的批准全部用于补充发行人二级资本。</t>
+          <t>本期债券的募集资金将根据适用法律和监管部门的批准用于补充发行人其他一级资本</t>
         </is>
       </c>
       <c r="AC95" s="3" t="inlineStr">
         <is>
-          <t>华泰联合证券有限责任公司,渤海银行股份有限公司,中国工商银行股份有限公司,华夏银行股份有限公司,中国邮政储蓄银行股份有限公司,恒丰银行股份有限公司,中国银行股份有限公司,招商证券股份有限公司,国泰海通证券股份有限公司,国开证券股份有限公司,广发证券股份有限公司</t>
+          <t>中信证券股份有限公司,国泰海通证券股份有限公司,中国国际金融股份有限公司,兴业银行股份有限公司,上海浦东发展银行股份有限公司,中信建投证券股份有限公司</t>
         </is>
       </c>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3" t="inlineStr">
         <is>
-          <t>二级资本工具</t>
+          <t>商业银行次级债券</t>
         </is>
       </c>
       <c r="AF95" s="3" t="inlineStr">
@@ -22289,7 +22295,7 @@
       </c>
       <c r="AH95" s="3" t="inlineStr">
         <is>
-          <t>广州银行股份有限公司2026年二级资本债券(第一期)</t>
+          <t>中原银行股份有限公司2026年无固定期限资本债券(第一期)</t>
         </is>
       </c>
       <c r="AI95" s="3" t="inlineStr">
@@ -22299,7 +22305,7 @@
       </c>
       <c r="AJ95" s="3" t="inlineStr">
         <is>
-          <t>2036-09-21</t>
+          <t>2031-09-21</t>
         </is>
       </c>
       <c r="AK95" s="3" t="inlineStr">
@@ -22354,7 +22360,7 @@
       </c>
       <c r="AU95" s="3" t="inlineStr">
         <is>
-          <t>2031-09-21</t>
+          <t/>
         </is>
       </c>
       <c r="AV95" s="3" t="inlineStr">
@@ -22364,12 +22370,12 @@
       </c>
       <c r="AW95" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX95" s="3" t="inlineStr">
         <is>
-          <t>二级资本工具</t>
+          <t>其他一级资本工具</t>
         </is>
       </c>
       <c r="AY95" s="3" t="inlineStr">
@@ -22382,7 +22388,7 @@
     <row r="96" customHeight="true" ht="18.0">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>26中原银行永续债01</t>
+          <t>大唐YK20</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
@@ -22392,64 +22398,64 @@
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>242680047.IB</t>
+          <t>246087.SH</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>5+N</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E96" s="4" t="n">
-        <v>100.0</v>
+        <v>25.0</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>100.0</v>
+        <v>25.0</v>
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.30</t>
+          <t>1.00 ~ 2.00</t>
         </is>
       </c>
       <c r="H96" s="4" t="n">
-        <v>1.92</v>
+        <v>1.59</v>
       </c>
       <c r="I96" s="4" t="n">
-        <v>50.94</v>
+        <v>33.21</v>
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="K96" s="3" t="inlineStr">
         <is>
-          <t>23中原银行永续债01</t>
+          <t>24大唐集MTN010</t>
         </is>
       </c>
       <c r="L96" s="3" t="inlineStr">
         <is>
-          <t>1.92Y+N</t>
+          <t>3.01Y+N</t>
         </is>
       </c>
       <c r="M96" s="3" t="inlineStr">
         <is>
-          <t>1.6755</t>
+          <t>1.7108</t>
         </is>
       </c>
       <c r="N96" s="3" t="inlineStr">
         <is>
-          <t>1.6600/--</t>
+          <t>1.7300/--</t>
         </is>
       </c>
       <c r="O96" s="3" t="inlineStr">
         <is>
-          <t>中原银行股份有限公司</t>
+          <t>中国大唐集团有限公司</t>
         </is>
       </c>
       <c r="P96" s="3" t="inlineStr">
         <is>
-          <t>B 51.97</t>
+          <t>B- 43.53</t>
         </is>
       </c>
       <c r="Q96" s="3" t="inlineStr">
@@ -22459,7 +22465,7 @@
       </c>
       <c r="R96" s="3" t="inlineStr">
         <is>
-          <t>09-17 09:00</t>
+          <t>09-17 16:00</t>
         </is>
       </c>
       <c r="S96" s="3" t="inlineStr">
@@ -22472,16 +22478,18 @@
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="U96" s="3"/>
+      <c r="U96" s="4" t="n">
+        <v>1.94</v>
+      </c>
       <c r="V96" s="3"/>
       <c r="W96" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X96" s="3" t="inlineStr">
         <is>
-          <t>1.88%~1.98%</t>
+          <t>1.60%~1.70%</t>
         </is>
       </c>
       <c r="Y96" s="3" t="inlineStr">
@@ -22496,38 +22504,38 @@
       </c>
       <c r="AA96" s="3" t="inlineStr">
         <is>
-          <t>河南省-郑州市</t>
+          <t>河北省-保定市</t>
         </is>
       </c>
       <c r="AB96" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金将根据适用法律和监管部门的批准用于补充发行人其他一级资本</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟将用于生产性支出,包括偿还有息债务、补充流动资金、项目投资及运营等符合法律法规要求的用途</t>
         </is>
       </c>
       <c r="AC96" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,国泰海通证券股份有限公司,中国国际金融股份有限公司,兴业银行股份有限公司,上海浦东发展银行股份有限公司,中信建投证券股份有限公司</t>
+          <t>中信证券股份有限公司,华泰联合证券有限责任公司,国泰海通证券股份有限公司,中国国际金融股份有限公司,中信建投证券股份有限公司,光大证券股份有限公司,申万宏源证券有限公司,中国银河证券股份有限公司</t>
         </is>
       </c>
       <c r="AD96" s="3"/>
       <c r="AE96" s="3" t="inlineStr">
         <is>
-          <t>商业银行次级债券</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF96" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>中央国有企业</t>
         </is>
       </c>
       <c r="AG96" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH96" s="3" t="inlineStr">
         <is>
-          <t>中原银行股份有限公司2026年无固定期限资本债券(第一期)</t>
+          <t>中国大唐集团有限公司2026年面向专业投资者公开发行科技创新可续期公司债券(第十期)</t>
         </is>
       </c>
       <c r="AI96" s="3" t="inlineStr">
@@ -22537,22 +22545,18 @@
       </c>
       <c r="AJ96" s="3" t="inlineStr">
         <is>
-          <t>2031-09-21</t>
-        </is>
-      </c>
-      <c r="AK96" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2029-09-21</t>
+        </is>
+      </c>
+      <c r="AK96" s="3"/>
       <c r="AL96" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t/>
         </is>
       </c>
       <c r="AM96" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AN96" s="3" t="inlineStr">
@@ -22562,32 +22566,32 @@
       </c>
       <c r="AO96" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP96" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AQ96" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR96" s="3" t="inlineStr">
         <is>
-          <t>商业银行</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AS96" s="3" t="inlineStr">
         <is>
-          <t>城商行</t>
+          <t>火电</t>
         </is>
       </c>
       <c r="AT96" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AU96" s="3" t="inlineStr">
@@ -22607,7 +22611,7 @@
       </c>
       <c r="AX96" s="3" t="inlineStr">
         <is>
-          <t>其他一级资本工具</t>
+          <t>次级债权</t>
         </is>
       </c>
       <c r="AY96" s="3" t="inlineStr">
@@ -22620,74 +22624,62 @@
     <row r="97" customHeight="true" ht="18.0">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>大唐YK20</t>
+          <t>26南K3EB</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>09-17 18:00</t>
+          <t>09-17 00:00</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>246087.SH</t>
+          <t>137209.SH</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E97" s="4" t="n">
-        <v>25.0</v>
+        <v>5.0</v>
       </c>
       <c r="F97" s="4" t="n">
-        <v>25.0</v>
-      </c>
-      <c r="G97" s="3" t="inlineStr">
-        <is>
-          <t>1.00 ~ 2.00</t>
-        </is>
-      </c>
+        <v>5.0</v>
+      </c>
+      <c r="G97" s="3"/>
       <c r="H97" s="4" t="n">
-        <v>1.59</v>
+        <v>0.1</v>
       </c>
       <c r="I97" s="4" t="n">
-        <v>33.21</v>
+        <v>-115.79</v>
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="K97" s="3" t="inlineStr">
-        <is>
-          <t>24大唐集MTN010</t>
-        </is>
-      </c>
-      <c r="L97" s="3" t="inlineStr">
-        <is>
-          <t>3.01Y+N</t>
-        </is>
-      </c>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="K97" s="3"/>
+      <c r="L97" s="3"/>
       <c r="M97" s="3" t="inlineStr">
         <is>
-          <t>1.7108</t>
+          <t>--</t>
         </is>
       </c>
       <c r="N97" s="3" t="inlineStr">
         <is>
-          <t>1.7300/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O97" s="3" t="inlineStr">
         <is>
-          <t>中国大唐集团有限公司</t>
+          <t>南山集团有限公司</t>
         </is>
       </c>
       <c r="P97" s="3" t="inlineStr">
         <is>
-          <t>B- 43.53</t>
+          <t>C+ 33.04</t>
         </is>
       </c>
       <c r="Q97" s="3" t="inlineStr">
@@ -22697,7 +22689,7 @@
       </c>
       <c r="R97" s="3" t="inlineStr">
         <is>
-          <t>09-17 16:00</t>
+          <t>09-17 00:00</t>
         </is>
       </c>
       <c r="S97" s="3" t="inlineStr">
@@ -22711,19 +22703,15 @@
         </is>
       </c>
       <c r="U97" s="4" t="n">
-        <v>1.94</v>
+        <v>1.0</v>
       </c>
       <c r="V97" s="3"/>
       <c r="W97" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
-        </is>
-      </c>
-      <c r="X97" s="3" t="inlineStr">
-        <is>
-          <t>1.60%~1.70%</t>
-        </is>
-      </c>
+          <t>6-</t>
+        </is>
+      </c>
+      <c r="X97" s="3"/>
       <c r="Y97" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -22736,28 +22724,32 @@
       </c>
       <c r="AA97" s="3" t="inlineStr">
         <is>
-          <t>河北省-保定市</t>
+          <t>山东省-烟台市</t>
         </is>
       </c>
       <c r="AB97" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟将用于生产性支出,包括偿还有息债务、补充流动资金、项目投资及运营等符合法律法规要求的用途</t>
+          <t>本期债券的募集资金拟全部用于偿还到期债务。</t>
         </is>
       </c>
       <c r="AC97" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,华泰联合证券有限责任公司,国泰海通证券股份有限公司,中国国际金融股份有限公司,中信建投证券股份有限公司,光大证券股份有限公司,申万宏源证券有限公司,中国银河证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD97" s="3"/>
+          <t>金圆统一证券有限公司</t>
+        </is>
+      </c>
+      <c r="AD97" s="3" t="inlineStr">
+        <is>
+          <t>南山集团有限公司</t>
+        </is>
+      </c>
       <c r="AE97" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>可交换债券</t>
         </is>
       </c>
       <c r="AF97" s="3" t="inlineStr">
         <is>
-          <t>中央国有企业</t>
+          <t>集体企业</t>
         </is>
       </c>
       <c r="AG97" s="3" t="inlineStr">
@@ -22767,12 +22759,12 @@
       </c>
       <c r="AH97" s="3" t="inlineStr">
         <is>
-          <t>中国大唐集团有限公司2026年面向专业投资者公开发行科技创新可续期公司债券(第十期)</t>
+          <t>南山集团有限公司2026年面向专业投资者非公开发行科技创新可交换公司债券(第二期)(品种一)</t>
         </is>
       </c>
       <c r="AI97" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ97" s="3" t="inlineStr">
@@ -22803,27 +22795,27 @@
       </c>
       <c r="AP97" s="3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ97" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>金属和非金属矿产</t>
         </is>
       </c>
       <c r="AR97" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>有色</t>
         </is>
       </c>
       <c r="AS97" s="3" t="inlineStr">
         <is>
-          <t>火电</t>
+          <t>常用有色金属</t>
         </is>
       </c>
       <c r="AT97" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>工业金属</t>
         </is>
       </c>
       <c r="AU97" s="3" t="inlineStr">
@@ -22833,17 +22825,17 @@
       </c>
       <c r="AV97" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW97" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX97" s="3" t="inlineStr">
         <is>
-          <t>次级债权</t>
+          <t>普通债权</t>
         </is>
       </c>
       <c r="AY97" s="3" t="inlineStr">
@@ -22856,132 +22848,140 @@
     <row r="98" customHeight="true" ht="18.0">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>26南K3EB</t>
+          <t>26电投K7</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>09-17 00:00</t>
+          <t>09-17 19:00</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>137209.SH</t>
+          <t>246128.SH</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>20Y</t>
         </is>
       </c>
       <c r="E98" s="4" t="n">
-        <v>5.0</v>
+        <v>20.0</v>
       </c>
       <c r="F98" s="4" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="G98" s="3"/>
+        <v>20.0</v>
+      </c>
+      <c r="G98" s="3" t="inlineStr">
+        <is>
+          <t>1.70 ~ 2.70</t>
+        </is>
+      </c>
       <c r="H98" s="4" t="n">
-        <v>0.1</v>
+        <v>2.25</v>
       </c>
       <c r="I98" s="4" t="n">
-        <v>-115.79</v>
+        <v>11.76</v>
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="K98" s="3" t="inlineStr">
+        <is>
+          <t>26电投K6</t>
+        </is>
+      </c>
+      <c r="L98" s="3" t="inlineStr">
+        <is>
+          <t>9.92Y</t>
+        </is>
+      </c>
+      <c r="M98" s="3" t="inlineStr">
+        <is>
+          <t>1.9686</t>
+        </is>
+      </c>
+      <c r="N98" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O98" s="3" t="inlineStr">
+        <is>
+          <t>国家电力投资集团有限公司</t>
+        </is>
+      </c>
+      <c r="P98" s="3" t="inlineStr">
+        <is>
+          <t>B- 44.43</t>
+        </is>
+      </c>
+      <c r="Q98" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="R98" s="3" t="inlineStr">
+        <is>
+          <t>09-17 15:00</t>
+        </is>
+      </c>
+      <c r="S98" s="3" t="inlineStr">
+        <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K98" s="3"/>
-      <c r="L98" s="3"/>
-      <c r="M98" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="N98" s="3" t="inlineStr">
-        <is>
-          <t>--/--</t>
-        </is>
-      </c>
-      <c r="O98" s="3" t="inlineStr">
-        <is>
-          <t>南山集团有限公司</t>
-        </is>
-      </c>
-      <c r="P98" s="3" t="inlineStr">
-        <is>
-          <t>C+ 33.04</t>
-        </is>
-      </c>
-      <c r="Q98" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="R98" s="3" t="inlineStr">
-        <is>
-          <t>09-17 00:00</t>
-        </is>
-      </c>
-      <c r="S98" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T98" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="U98" s="4" t="n">
-        <v>1.0</v>
+        <v>3.99</v>
       </c>
       <c r="V98" s="3"/>
       <c r="W98" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
-        </is>
-      </c>
-      <c r="X98" s="3"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X98" s="3" t="inlineStr">
+        <is>
+          <t>2.20%~2.30%</t>
+        </is>
+      </c>
       <c r="Y98" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z98" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z98" s="3"/>
       <c r="AA98" s="3" t="inlineStr">
         <is>
-          <t>山东省-烟台市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB98" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金拟全部用于偿还到期债务。</t>
+          <t>本期债券募集资金扣除发行等相关费用后,拟用于生产性支出,包括偿还有息债务、补充流动资金等符合法律法规要求的用途</t>
         </is>
       </c>
       <c r="AC98" s="3" t="inlineStr">
         <is>
-          <t>金圆统一证券有限公司</t>
-        </is>
-      </c>
-      <c r="AD98" s="3" t="inlineStr">
-        <is>
-          <t>南山集团有限公司</t>
-        </is>
-      </c>
+          <t>东方证券股份有限公司,中银国际证券股份有限公司,国泰海通证券股份有限公司,中泰证券股份有限公司,光大证券股份有限公司,平安证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD98" s="3"/>
       <c r="AE98" s="3" t="inlineStr">
         <is>
-          <t>可交换债券</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF98" s="3" t="inlineStr">
         <is>
-          <t>集体企业</t>
+          <t>中央国有企业</t>
         </is>
       </c>
       <c r="AG98" s="3" t="inlineStr">
@@ -22991,73 +22991,73 @@
       </c>
       <c r="AH98" s="3" t="inlineStr">
         <is>
-          <t>南山集团有限公司2026年面向专业投资者非公开发行科技创新可交换公司债券(第二期)(品种一)</t>
+          <t>国家电力投资集团有限公司2026年面向专业投资者公开发行科技创新公司债券(第七期)</t>
         </is>
       </c>
       <c r="AI98" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ98" s="3" t="inlineStr">
         <is>
-          <t>2029-09-21</t>
+          <t>2046-09-18</t>
         </is>
       </c>
       <c r="AK98" s="3"/>
       <c r="AL98" s="3" t="inlineStr">
         <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AM98" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AN98" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="AO98" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP98" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AQ98" s="3" t="inlineStr">
+        <is>
+          <t>公用事业</t>
+        </is>
+      </c>
+      <c r="AR98" s="3" t="inlineStr">
+        <is>
+          <t>电力</t>
+        </is>
+      </c>
+      <c r="AS98" s="3" t="inlineStr">
+        <is>
+          <t>其他电力</t>
+        </is>
+      </c>
+      <c r="AT98" s="3" t="inlineStr">
+        <is>
+          <t>电力</t>
+        </is>
+      </c>
+      <c r="AU98" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM98" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="AN98" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="AO98" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP98" s="3" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="AQ98" s="3" t="inlineStr">
-        <is>
-          <t>金属和非金属矿产</t>
-        </is>
-      </c>
-      <c r="AR98" s="3" t="inlineStr">
-        <is>
-          <t>有色</t>
-        </is>
-      </c>
-      <c r="AS98" s="3" t="inlineStr">
-        <is>
-          <t>常用有色金属</t>
-        </is>
-      </c>
-      <c r="AT98" s="3" t="inlineStr">
-        <is>
-          <t>工业金属</t>
-        </is>
-      </c>
-      <c r="AU98" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV98" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW98" s="3" t="inlineStr">
